--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v1.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v1.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,9 +72,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="008C8C8C"/>
     </font>
     <font>
       <color rgb="00000000"/>
@@ -201,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,9 +220,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -241,19 +235,19 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -272,13 +266,13 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -933,7 +927,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>시트 양식만 — 시나리오(data/scenarios.yaml)는 ③단계</t>
+          <t>실제 사고 기반 공격 흐름 8개</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1119,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>0/35개 작성 — 문구는 ③단계(요약설명 자리에 영문명 회색 표시, 대표 사례는 사고 DB·ATLAS 근거, 핵심 대응은 NIST 통제) | scripts/validate.py 세부위협 35개 · 사고 31건 · 실제 사고가 매핑된 행 22개</t>
+          <t>35/35개 작성 — 전 항목 완료 | scripts/validate.py 세부위협 35개(문구 35) · 사고 31건 · 시나리오 8개 · 실제 사고가 매핑된 행 22개 · 인용 사례 45건</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5446,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>CNN·The Standard 〈홍콩 딥페이크 금융사기〉</t>
+          <t>CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -7185,7 +7179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7231,7 +7225,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -7241,29 +7235,29 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
+          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
+          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -7273,29 +7267,29 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>위험평가 결과</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
+          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -7305,29 +7299,29 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
+          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
+          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -7337,29 +7331,29 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
+          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -7369,22 +7363,22 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>위험평가 결과</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
+          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
         </is>
       </c>
     </row>
@@ -7401,22 +7395,22 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>분류 체계(data/taxonomy.yaml)</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
         </is>
       </c>
     </row>
@@ -7433,22 +7427,22 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py · taxonomy_rules.py</t>
+          <t>사고 DB(data/incidents.yaml)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7459,116 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
+          <t>교차 매핑</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>참조 추출본(reference/)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>scripts/validate.py · taxonomy_rules.py</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>작업방향 D3~D9·D11·D12</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>emerging/작업방향.md 10장 권장안을 ①단계 착수 결정으로 확정 — D3(킬체인 7단계+AI 역할·자율성)·D4(발생가능성에 AI 역량 성숙도 신호)·D8(재인용+신규)·D9(통합본 뷰 Lv0, ④단계)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인). D5~D7은 영역 2(enterprise) 결정이라 영역 2 착수 시 확정</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>사용자 지침 — 남은 결정은 착수 시 확정</t>
         </is>
@@ -7619,12 +7709,12 @@
           <t>단일 자율 공격 에이전트 실행</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Single autonomous attack agent execution</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>단일 자율 에이전트가 정찰~실행을 사람 속도 밖에서 수행</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -7664,7 +7754,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AU-6·CA-7</t>
+          <t>사람 속도를 넘는 반복·연쇄 행위 시퀀스와 비정상 세션 속도를 행위 기반으로 탐지(NIST SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -7687,12 +7777,12 @@
           <t>AI 가속 자격증명 탈취·내부 확산</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated credential theft and lateral movement</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>AI 가속 자격증명 탈취·측면 이동으로 클라우드 전반 급속 장악</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -7732,7 +7822,7 @@
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-2·AC-6·SI-4</t>
+          <t>자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)</t>
         </is>
       </c>
     </row>
@@ -7755,12 +7845,12 @@
           <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous agent mass-exploitation of CI/CD and workflows</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -7800,7 +7890,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CM-7·SA-15</t>
+          <t>워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -7823,12 +7913,12 @@
           <t>AI 개발 도구 신뢰·설정 악용</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of trust and configuration in AI development tools</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -7868,7 +7958,7 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·SA-15</t>
+          <t>AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7981,12 @@
           <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of victim-side AI CLIs and local agents</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -7936,7 +8026,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·CM-7</t>
+          <t>AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -7959,12 +8049,12 @@
           <t>딥페이크 기반 생체·본인확인 우회</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Deepfake-based biometric and identity verification bypass</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8004,7 +8094,7 @@
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST IA-2·AC-2</t>
+          <t>라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8117,12 @@
           <t>AI 가속 대규모 데이터 탈취·반출</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated large-scale data theft and exfiltration</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 자동 수집·반출로 대규모 데이터 유출</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8072,7 +8162,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AU-6·SC-7</t>
+          <t>대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8185,12 @@
           <t>영상 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Video deepfake impersonation</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8140,7 +8230,7 @@
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·IA-2</t>
+          <t>고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)</t>
         </is>
       </c>
     </row>
@@ -8163,12 +8253,12 @@
           <t>AI 생성·AI 연동 악성코드</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated and AI-integrated malware</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8208,7 +8298,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4·SI-7</t>
+          <t>시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8231,12 +8321,12 @@
           <t>공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Building offensive AI agents and attack harnesses</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8276,7 +8366,7 @@
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·PM-16·SA-11</t>
+          <t>AI 에이전트 특유의 빠른·반복적 행위 시퀀스와 도구 연쇄 호출을 행위 기반으로 탐지(NIST SI-4·PM-16)</t>
         </is>
       </c>
     </row>
@@ -8299,12 +8389,12 @@
           <t>다중 에이전트 공격 조율</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Multi-agent attack orchestration</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -8344,7 +8434,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AU-6·CA-7</t>
+          <t>동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8457,12 @@
           <t>AI 인프라 악용 크립토재킹</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cryptojacking via abused AI infrastructure</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>노출·오설정 AI 인프라 악용 크립토재킹으로 자원 탈취</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8412,7 +8502,7 @@
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·AC-6·CM-7</t>
+          <t>AI 인프라의 비정상 자원 사용·외부 노출·무인증 접근을 모니터링(NIST SI-4·CM-7)</t>
         </is>
       </c>
     </row>
@@ -8435,12 +8525,12 @@
           <t>딥페이크·AI 사칭 기반 금전 사기</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial fraud via deepfake and AI impersonation</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8480,7 +8570,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·IA-2</t>
+          <t>고액·비정상 송금 요청과 사칭 징후를 결제·승인 흐름에서 모니터링(NIST IA-2)</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8593,12 @@
           <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated wiper and destructive scripts</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8548,7 +8638,7 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-7·CP-9</t>
+          <t>대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8661,12 @@
           <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Malware generating commands dynamically from AI at runtime</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8616,7 +8706,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4·AU-6</t>
+          <t>LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8639,12 +8729,12 @@
           <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Covert C2 via AI service APIs and web interfaces</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8684,7 +8774,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4·AU-6</t>
+          <t>AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8797,12 @@
           <t>AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI vulnerability discovery (bug hunting)</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8752,7 +8842,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SA-11·SI-7</t>
+          <t>자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -8775,12 +8865,12 @@
           <t>AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI exploit generation and development</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -8820,7 +8910,7 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SI-7·SA-11</t>
+          <t>공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -8843,12 +8933,12 @@
           <t>LLMjacking·AI 과금 폭탄</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) LLMjacking and AI cost-harvesting</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>탈취 자격증명으로 관리형 LLM·GPU 무단 사용(LLMjacking)</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8888,7 +8978,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AC-2·AC-6·SI-4</t>
+          <t>관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8911,12 +9001,12 @@
           <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Agent-driven identification of exposed assets and attack surface</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -8956,7 +9046,7 @@
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·SC-7·SI-4</t>
+          <t>외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)</t>
         </is>
       </c>
     </row>
@@ -8979,12 +9069,12 @@
           <t>음성 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Voice deepfake impersonation</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9024,7 +9114,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·IA-2</t>
+          <t>헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9137,12 @@
           <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Hidden-instruction injection into AI coding tool rules and configs</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9092,7 +9182,7 @@
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SA-15·SI-7·CM-7</t>
+          <t>규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)</t>
         </is>
       </c>
     </row>
@@ -9115,12 +9205,12 @@
           <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven collection and triage of vulnerability intel and public PoCs</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9160,7 +9250,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST RA-5·PM-16</t>
+          <t>자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9183,12 +9273,12 @@
           <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated mass phishing and lures</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9228,7 +9318,7 @@
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·SI-4·SC-7</t>
+          <t>발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9251,12 +9341,12 @@
           <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven defense evasion and obfuscation</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9296,7 +9386,7 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4·SI-7</t>
+          <t>행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9319,12 +9409,12 @@
           <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated attack tools, scripts and shell commands</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9364,7 +9454,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-3·SI-4·PM-16</t>
+          <t>실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9387,12 +9477,12 @@
           <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven OSINT and target profiling</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9432,7 +9522,7 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST PM-16·AT-2(3)·SI-4</t>
+          <t>자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9545,12 @@
           <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of dark LLMs and jailbroken models</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9500,7 +9590,7 @@
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST PM-16·SI-4</t>
+          <t>지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9613,12 @@
           <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted analysis of target environment and relationships</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9568,7 +9658,7 @@
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST PM-16·SI-4</t>
+          <t>공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9591,12 +9681,12 @@
           <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scaling and mass-production of AI-enabled attacks</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9636,7 +9726,7 @@
       </c>
       <c r="N34" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SI-4·CA-7·PM-16</t>
+          <t>캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9749,12 @@
           <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven targeted spear-phishing and BEC</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9704,7 +9794,7 @@
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·SI-4</t>
+          <t>고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9727,12 +9817,12 @@
           <t>공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of attack infrastructure and AI service proxies</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9772,7 +9862,7 @@
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SC-7·SI-4</t>
+          <t>AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)</t>
         </is>
       </c>
     </row>
@@ -9795,12 +9885,12 @@
           <t>AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted code audit and fuzzing</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9840,7 +9930,7 @@
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST SA-11·SA-15·RA-5</t>
+          <t>의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9953,12 @@
           <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI lures, ClickFix and crafted links to induce execution</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -9908,7 +9998,7 @@
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST AT-2(3)·SI-4</t>
+          <t>에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)</t>
         </is>
       </c>
     </row>
@@ -9931,12 +10021,12 @@
           <t>증류·파인튜닝으로 공세 역량 확보</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Distillation and fine-tuning to obtain offensive capability</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>증류·파인튜닝으로 가드레일 제거한 공세 모델 확보 정황</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -9976,7 +10066,7 @@
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>대응 기준: NIST PM-16</t>
+          <t>모델 가중치·데이터 유출과 비정상 대량 질의(증류 정황)를 자사 AI 자산에서 모니터링(NIST PM-16)</t>
         </is>
       </c>
     </row>
@@ -10012,49 +10102,49 @@
       </c>
     </row>
     <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>[RT] 정찰·표적 분석
 Reconnaissance &amp; Target Analysis
 (4)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>[RD] 공격 역량 확보
 Resource Development &amp; Weaponization
 (5)</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>[VE] 취약점 발굴·익스플로잇 생성
 Vulnerability Discovery &amp; Exploit Generation
 (5)</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>[IA] 초기 침투·사회공학
 Initial Access &amp; Social Engineering
 (6)</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>[AO] 자율 실행·확산
 Autonomous Operations &amp; Lateral Movement
 (6)</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>[CC] 은닉·명령제어
 Evasion &amp; Command-and-Control
 (4)</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>[IM] 영향·규모화
 Impact &amp; Scaling
@@ -10063,187 +10153,187 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>AIA-RT-02 AI 에이전트의 노출 자산·공격면 자동 식별 [1]</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>AIA-RD-04 공세 AI 에이전트·공격 하네스 구축 [2]</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>AIA-VE-03.1 AI 생성·AI 연동 악성코드 [2]</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>AIA-IA-02.1 영상 딥페이크 사칭 [2]</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-01 단일 자율 공격 에이전트 실행 [4]</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>AIA-CC-01 AI 서비스 API·웹 인터페이스 경유 은닉 C2 [1]</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="17" t="inlineStr">
         <is>
           <t>AIA-IM-02 AI 가속 대규모 데이터 탈취·반출 [2]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>AIA-RT-03 AI 기반 취약점 정보·공개 PoC 자동 수집·분류 [1]</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>AIA-RD-01.1 다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>AIA-VE-03.2 AI 생성 와이퍼·파괴 스크립트 [1]</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>AIA-IA-03 딥페이크 기반 생체·본인확인 우회 [2]</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-04 자율 에이전트의 CI/CD·워크플로 대량 악용 [3]</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>AIA-CC-02 실행 중 AI 명령 동적 생성 악성코드 [1]</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>AIA-IM-03.1 AI 인프라 악용 크립토재킹 [2]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>AIA-RT-01.1 AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>AIA-RD-02 AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>AIA-VE-01.1 AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>AIA-IA-01.1 AI 생성 대량 피싱·미끼 [1]</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-05 AI 가속 자격증명 탈취·내부 확산 [3]</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>AIA-CC-04 AI 코딩 도구 규칙·설정 숨은 지시 주입 [1]</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>AIA-IM-01 딥페이크·AI 사칭 기반 금전 사기 [1]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>AIA-RT-01.2 AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>AIA-RD-03 공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>AIA-VE-02 AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>AIA-IA-02.2 음성 딥페이크 사칭 [1]</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-02 다중 에이전트 공격 조율 [2]</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>AIA-CC-03 AI 기반 방어 회피·난독화</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>AIA-IM-03.2 LLMjacking·AI 과금 폭탄 [1]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>AIA-RD-01.2 증류·파인튜닝으로 공세 역량 확보</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>AIA-VE-01.2 AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>AIA-IA-01.2 AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-03.1 피해 단말의 AI CLI·로컬 에이전트 악용 [2]</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>AIA-IM-04 AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>AIA-IA-04 AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>AIA-AO-03.2 AI 개발 도구 신뢰·설정 악용 [2]</t>
         </is>
@@ -10310,7 +10400,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>AI 활용 공격 보안위협 매트릭스 v1 — 분류·고유 축·교차 매핑·위험 평가·실제 근거</t>
         </is>
@@ -10324,32 +10414,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>분류 체계</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J3" s="22" t="inlineStr">
         <is>
           <t>고유 축</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="23" t="inlineStr">
         <is>
           <t>교차 매핑</t>
         </is>
       </c>
-      <c r="Z3" s="25" t="inlineStr">
+      <c r="Z3" s="24" t="inlineStr">
         <is>
           <t>위험 평가</t>
         </is>
       </c>
-      <c r="AF3" s="26" t="inlineStr">
+      <c r="AF3" s="25" t="inlineStr">
         <is>
           <t>실제 근거</t>
         </is>
       </c>
-      <c r="AP3" s="27" t="inlineStr">
+      <c r="AP3" s="26" t="inlineStr">
         <is>
           <t>대응 기준·참고 문헌</t>
         </is>
@@ -10598,10 +10688,15 @@
           <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven OSINT and target profiling</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LLM으로 업무용 SNS·논문·코드 저장소·보도자료를 대량 수집·요약해 핵심 인력과 그 관계·약점을 빠르게 추려낼 수 있음
+- 열람 자체는 합법이라 막기 어렵고, AI가 사람보다 빠르게 표적 명단을 만들어 후속 사회공학·침투의 발판이 됨</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -10616,7 +10711,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -10695,7 +10790,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB5" s="14" t="inlineStr">
+      <c r="AB5" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10734,7 +10829,7 @@
       <c r="AL5" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AM5" s="28" t="inlineStr">
+      <c r="AM5" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -10748,7 +10843,17 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ5" s="9" t="inlineStr"/>
+      <c r="AQ5" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)
+- 특정 부서·인력에 몰리는 외부 접촉·채용 제안의 반복 출처를 식별
+■ 대응
+- 핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)
+- 공개정보가 AI 정찰·표적 선정에 쓰이는 방식과 의심 접근 신고 경로를 교육(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR5" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -10776,10 +10881,15 @@
           <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted analysis of target environment and relationships</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 수집한 조직도·거래 관계·내부 용어를 AI로 상관분석해 설득력 있는 사칭 시나리오와 표적 우선순위를 만들 수 있음
+- 외부에서 보이는 관계만으로도 맥락이 재구성되어, 피해는 뒤따르는 사회공학·침투 단계에서 커짐</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -10794,7 +10904,7 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -10866,7 +10976,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB6" s="14" t="inlineStr">
+      <c r="AB6" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -10905,7 +11015,7 @@
       <c r="AL6" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="AM6" s="29" t="inlineStr">
+      <c r="AM6" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -10918,7 +11028,17 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ6" s="9" t="inlineStr"/>
+      <c r="AQ6" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)
+- 경영진·재무·조달 등 고가치 역할에 대한 외부 정보 수집 정황을 모니터링
+■ 대응
+- 조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)
+- 사칭 시나리오를 전제한 다채널 확인 절차를 고위험 승인에 적용(NIST SI-4)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR6" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -10946,10 +11066,15 @@
           <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Agent-driven identification of exposed assets and attack surface</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 에이전트로 인터넷 스캔·FOFA 조회를 자동화해 노출된 서비스·관리 인터페이스를 사람보다 빠르게 열거할 수 있음
+- 공격 가능 진입점 목록이 자동 생성돼 정찰-침투 간격이 짧아지고, 탐지·패치 전 선제 악용 위험이 커짐</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -10964,7 +11089,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -11036,7 +11161,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB7" s="14" t="inlineStr">
+      <c r="AB7" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11075,7 +11200,7 @@
       <c r="AL7" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM7" s="30" t="inlineStr">
+      <c r="AM7" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11093,7 +11218,17 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ7" s="9" t="inlineStr"/>
+      <c r="AQ7" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)
+- 관리 인터페이스·디버그 엔드포인트의 외부 노출을 상시 점검
+■ 대응
+- 공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)
+- 노출 자산 인벤토리와 신속 패치로 자율 열거-악용 간격을 좁힘(NIST RA-5)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
       <c r="AR7" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
@@ -11121,10 +11256,15 @@
           <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven collection and triage of vulnerability intel and public PoCs</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 공개 취약점 정보와 PoC를 자동 수집·분류해 공격에 쓸 형태로 빠르게 정리할 수 있음
+- 공개 즉시 악용되는 빠른 n-day를 가속해, 패치 전 노출 구간에서 피해 위험이 커짐</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -11139,7 +11279,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -11210,7 +11350,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB8" s="14" t="inlineStr">
+      <c r="AB8" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11249,7 +11389,7 @@
       <c r="AL8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AM8" s="30" t="inlineStr">
+      <c r="AM8" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -11266,7 +11406,17 @@
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ8" s="9" t="inlineStr"/>
+      <c r="AQ8" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)
+- 공개 직후 집중되는 탐침·악용 시도를 모니터링
+■ 대응
+- 공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)
+- 위협 인텔로 악용 가능성이 높은 취약점을 선별 대응(NIST PM-16)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
       <c r="AR8" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
@@ -11294,10 +11444,15 @@
           <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of dark LLMs and jailbroken models</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 지하 시장에서 가드레일이 제거된 공세 특화·탈옥 LLM을 구해 역량이 낮아도 피싱·악성코드 제작에 접근할 수 있음
+- 도구 확보 단계라 단독 피해는 없지만, 공격자 저변이 넓어져 후속 단계 전반의 빈도를 끌어올림</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -11312,7 +11467,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -11382,7 +11537,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB9" s="14" t="inlineStr">
+      <c r="AB9" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11421,7 +11576,7 @@
       <c r="AL9" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="AM9" s="28" t="inlineStr">
+      <c r="AM9" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -11434,7 +11589,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ9" s="9" t="inlineStr"/>
+      <c r="AQ9" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)
+■ 대응
+- 공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR9" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -11462,10 +11625,15 @@
           <t>증류·파인튜닝으로 공세 역량 확보</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Distillation and fine-tuning to obtain offensive capability</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>증류·파인튜닝으로 가드레일 제거한 공세 모델 확보 정황</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 상용 모델을 증류·파인튜닝해 안전장치를 약화시킨 공세 모델을 만들려 시도할 수 있음
+- 아직 연구·시연 수준이라 직접 피해는 제한적이나, 성공 시 탐지가 어려운 전용 역량이 됨</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -11480,7 +11648,7 @@
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -11542,7 +11710,7 @@
           <t>하</t>
         </is>
       </c>
-      <c r="AB10" s="15" t="inlineStr">
+      <c r="AB10" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -11581,7 +11749,7 @@
       <c r="AL10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM10" s="29" t="inlineStr">
+      <c r="AM10" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -11593,7 +11761,15 @@
           <t>PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ10" s="9" t="inlineStr"/>
+      <c r="AQ10" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 모델 가중치·데이터 유출과 비정상 대량 질의(증류 정황)를 자사 AI 자산에서 모니터링(NIST PM-16)
+■ 대응
+- 자사 모델·데이터의 유출·추출을 통제해 공세 파생 모델의 재료가 되지 않게 함(NIST PM-16)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR10" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -11621,10 +11797,15 @@
           <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated attack tools, scripts and shell commands</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 스캐너·셸 명령·HTTP 탐침 같은 도구·스크립트를 즉석에서 생성해 공격 준비 시간을 줄일 수 있음
+- 단독 피해는 없으나 침투·실행 단계를 가속해 전체 공격 속도를 높임</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -11639,7 +11820,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -11711,7 +11892,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB11" s="14" t="inlineStr">
+      <c r="AB11" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11750,7 +11931,7 @@
       <c r="AL11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="AM11" s="28" t="inlineStr">
+      <c r="AM11" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -11764,7 +11945,15 @@
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ11" s="9" t="inlineStr"/>
+      <c r="AQ11" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
       <c r="AR11" s="9" t="inlineStr">
         <is>
           <t>Unit 42 〈Hermes Agent〉</t>
@@ -11792,10 +11981,15 @@
           <t>공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of attack infrastructure and AI service proxies</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취·중계 계정이나 서버리스로 AI 서비스를 익명 경유하는 공격 인프라를 세워 출처·비용을 숨길 수 있음
+- 정상 서비스·인프라를 경유해 경계 통제가 걸러내기 어렵고, 후속 C2·대량 공격의 기반이 됨</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -11810,7 +12004,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -11887,7 +12081,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB12" s="14" t="inlineStr">
+      <c r="AB12" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -11926,7 +12120,7 @@
       <c r="AL12" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM12" s="29" t="inlineStr">
+      <c r="AM12" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -11939,7 +12133,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ12" s="9" t="inlineStr"/>
+      <c r="AQ12" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)
+■ 대응
+- AI 서비스 egress 가시성을 확보하고 비인가 AI 트래픽·신규 인프라 접속을 통제(NIST SC-7)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR12" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -11967,10 +12169,15 @@
           <t>공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Building offensive AI agents and attack harnesses</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 스캐너·브라우저 자동화·침투 도구를 MCP 등으로 엮은 공격 프레임워크나 탈옥 모델 기반 자율 하네스를 구축할 수 있음
+- 한 번 만들면 사람 감독을 최소화한 반복·대규모 공격의 토대가 되어 피해 범위를 가늠하기 어려움</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -11985,7 +12192,7 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -12052,7 +12259,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB13" s="12" t="inlineStr">
+      <c r="AB13" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -12091,7 +12298,7 @@
       <c r="AL13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM13" s="30" t="inlineStr">
+      <c r="AM13" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12113,7 +12320,15 @@
 SA-11 Developer Testing and Evaluation</t>
         </is>
       </c>
-      <c r="AQ13" s="9" t="inlineStr"/>
+      <c r="AQ13" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 에이전트 특유의 빠른·반복적 행위 시퀀스와 도구 연쇄 호출을 행위 기반으로 탐지(NIST SI-4·PM-16)
+■ 대응
+- AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)
+- 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
+        </is>
+      </c>
       <c r="AR13" s="9" t="inlineStr">
         <is>
           <t>Anthropic 〈GTG-1002〉
@@ -12142,10 +12357,15 @@
           <t>AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI vulnerability discovery (bug hunting)</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 자율 AI 에이전트로 사람 개입 없이 미공개 취약점을 찾아내 대규모 표적에서 0-day를 양산할 수 있음
+- 같은 역량이 방어에도 쓰이지만, 공격자가 선점하면 패치 전 노출 구간에서 광범위한 악용으로 이어질 수 있음</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -12160,7 +12380,7 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -12231,7 +12451,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB14" s="13" t="inlineStr">
+      <c r="AB14" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12270,7 +12490,7 @@
       <c r="AL14" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM14" s="28" t="inlineStr">
+      <c r="AM14" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -12289,7 +12509,15 @@
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ14" s="9" t="inlineStr"/>
+      <c r="AQ14" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)
+■ 대응
+- 자체 AI 보조 취약점 발굴·퍼징으로 공격자보다 먼저 찾고(NIST SA-11), 신속 패치·무결성 검증으로 노출 구간을 좁힘(NIST SI-7·RA-5)
+- 참고: The Record 〈Big Sleep〉 · AppSecSanta 〈AI Pentesting Agents 2026〉</t>
+        </is>
+      </c>
       <c r="AR14" s="9" t="inlineStr">
         <is>
           <t>The Record 〈Big Sleep〉
@@ -12318,10 +12546,15 @@
           <t>AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted code audit and fuzzing</t>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 코드 리뷰·퍼징을 가속해 취약점 발견 속도를 높일 수 있음
+- 방어·공격 양용이라 단독 피해보다 발굴 단계를 증폭하며, 공급망 구성요소까지 넓게 겨냥될 수 있음</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -12336,7 +12569,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -12410,7 +12643,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB15" s="14" t="inlineStr">
+      <c r="AB15" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -12449,7 +12682,7 @@
       <c r="AL15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="AM15" s="29" t="inlineStr">
+      <c r="AM15" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -12468,7 +12701,15 @@
 RA-5 Vulnerability Monitoring and Scanning</t>
         </is>
       </c>
-      <c r="AQ15" s="9" t="inlineStr"/>
+      <c r="AQ15" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)
+■ 대응
+- 개발 단계에 AI 보조 테스트를 통합해 선제 발견하고(NIST SA-11·SA-15), 취약 구성요소를 신속 교체(NIST RA-5)
+- 참고: AppSecSanta 〈AI Pentesting Agents 2026〉</t>
+        </is>
+      </c>
       <c r="AR15" s="9" t="inlineStr">
         <is>
           <t>AppSecSanta 〈AI Pentesting Agents 2026〉</t>
@@ -12496,10 +12737,15 @@
           <t>AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI exploit generation and development</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 익스플로잇을 자동 생성·개발해, 공개 취약점을 사람 개입 없이 빠르게 무기화할 수 있음
+- 익스플로잇 개발 병목이 사라지면 공개 취약점이 즉시 악용돼 패치 전 노출 위험이 커짐</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -12514,7 +12760,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -12585,7 +12831,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB16" s="13" t="inlineStr">
+      <c r="AB16" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12624,7 +12870,7 @@
       <c r="AL16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM16" s="28" t="inlineStr">
+      <c r="AM16" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -12643,7 +12889,15 @@
 SA-11 Developer Testing and Evaluation</t>
         </is>
       </c>
-      <c r="AQ16" s="9" t="inlineStr"/>
+      <c r="AQ16" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)
+■ 대응
+- 신속 패치·가상 패치와 무결성 검증으로 즉시 무기화에 대응하고(NIST SI-7), 자체 익스플로잇 가능성 평가로 우선순위화(NIST SA-11·RA-5)
+- 참고: securityonline 〈GTIG AI 0-day〉</t>
+        </is>
+      </c>
       <c r="AR16" s="9" t="inlineStr">
         <is>
           <t>securityonline 〈GTIG AI 0-day〉</t>
@@ -12671,10 +12925,15 @@
           <t>AI 생성·AI 연동 악성코드</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated and AI-integrated malware</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 생성형 AI로 악성코드를 개발·변형해 시그니처 기반 탐지를 빠르게 무력화할 수 있음
+- 변종 양산이 쉬워져 정적 분석·시그니처가 따라가기 어렵고, 금전·첩보 목적에 두루 쓰임</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -12689,7 +12948,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -12760,7 +13019,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB17" s="12" t="inlineStr">
+      <c r="AB17" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -12799,7 +13058,7 @@
       <c r="AL17" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM17" s="30" t="inlineStr">
+      <c r="AM17" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -12821,7 +13080,15 @@
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ17" s="9" t="inlineStr"/>
+      <c r="AQ17" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)
+■ 대응
+- 행위 기반 EDR·실행 통제로 변종에 대응하고(NIST SI-3), 무결성 검증으로 변조를 차단(NIST SI-7)
+- 참고: securityonline 〈GTIG AI 0-day〉</t>
+        </is>
+      </c>
       <c r="AR17" s="9" t="inlineStr">
         <is>
           <t>securityonline 〈GTIG AI 0-day〉</t>
@@ -12849,10 +13116,15 @@
           <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated wiper and destructive scripts</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LLM으로 와이퍼·파괴 스크립트를 맞춤 생성·변형해 파괴형 공격을 빠르게 전개할 수 있음
+- 맞춤 생성으로 탐지·복구가 어려워지고, 기반시설 대상 시 운영·안전에 큰 피해가 날 수 있음</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -12867,7 +13139,7 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -12942,7 +13214,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB18" s="13" t="inlineStr">
+      <c r="AB18" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -12981,7 +13253,7 @@
       <c r="AL18" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM18" s="30" t="inlineStr">
+      <c r="AM18" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13003,7 +13275,15 @@
 CP-9 System Backup</t>
         </is>
       </c>
-      <c r="AQ18" s="9" t="inlineStr"/>
+      <c r="AQ18" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)
+■ 대응
+- 행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)
+- 참고: CERT Polska 〈Energy Report 2025〉</t>
+        </is>
+      </c>
       <c r="AR18" s="9" t="inlineStr">
         <is>
           <t>CERT Polska 〈Energy Report 2025〉</t>
@@ -13031,10 +13311,15 @@
           <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated mass phishing and lures</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 문법·맥락이 자연스러운 피싱 미끼를 대량 생성해, 오탈자·어색함에 기대던 기존 탐지를 무력화할 수 있음
+- 품질·규모가 함께 올라가 더 많은 표적이 속고, 피해는 계정 탈취·BEC로 이어짐</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -13049,7 +13334,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -13125,7 +13410,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB19" s="14" t="inlineStr">
+      <c r="AB19" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13164,7 +13449,7 @@
       <c r="AL19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM19" s="30" t="inlineStr">
+      <c r="AM19" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13186,7 +13471,16 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AQ19" s="9" t="inlineStr"/>
+      <c r="AQ19" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)
+- 디바이스 코드·OAuth 동의 등 비정상 인증 흐름을 모니터링(NIST SC-7)
+■ 대응
+- 피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR19" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -13214,10 +13508,15 @@
           <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven targeted spear-phishing and BEC</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 수집한 표적 정보를 AI로 엮어 맥락에 맞는 사칭 메시지를 만들어 특정 인물을 노릴 수 있음
+- 개인화 품질이 높아 의심을 사기 어렵고, 송금·자격증명 탈취로 직결될 수 있음</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -13232,7 +13531,7 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -13308,7 +13607,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB20" s="14" t="inlineStr">
+      <c r="AB20" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13347,7 +13646,7 @@
       <c r="AL20" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM20" s="28" t="inlineStr">
+      <c r="AM20" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -13360,7 +13659,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ20" s="9" t="inlineStr"/>
+      <c r="AQ20" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)
+■ 대응
+- 고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR20" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -13388,10 +13695,15 @@
           <t>영상 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Video deepfake impersonation</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 공개 영상으로 만든 영상 딥페이크로 경영진·동료를 사칭해 화상회의·면접에서 지시·신뢰를 얻을 수 있음
+- 사람의 시각 신뢰를 직접 무너뜨려 고액 송금·내부 접근 같은 큰 피해로 직결됨</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -13406,7 +13718,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -13472,7 +13784,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB21" s="12" t="inlineStr">
+      <c r="AB21" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -13511,7 +13823,7 @@
       <c r="AL21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM21" s="30" t="inlineStr">
+      <c r="AM21" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13532,10 +13844,18 @@
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ21" s="9" t="inlineStr"/>
+      <c r="AQ21" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)
+■ 대응
+- 고위험 요청에 다채널·사전 등록 경로 확인을 의무화하고 사용자 교육(NIST AT-2(3)·IA-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
+        </is>
+      </c>
       <c r="AR21" s="9" t="inlineStr">
         <is>
-          <t>CNN·The Standard 〈홍콩 딥페이크 금융사기〉</t>
+          <t>CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
       </c>
     </row>
@@ -13560,10 +13880,15 @@
           <t>음성 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Voice deepfake impersonation</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 직원·임원 목소리를 딥페이크로 흉내 내 전화 본인확인·헬프데스크 절차를 우회하고 추가 인증·승인을 받아낼 수 있음
+- 음성 신뢰에 기대던 절차가 뚫려 계정 등록·접근 확대로 이어짐</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -13578,7 +13903,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -13652,7 +13977,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB22" s="14" t="inlineStr">
+      <c r="AB22" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -13691,7 +14016,7 @@
       <c r="AL22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM22" s="30" t="inlineStr">
+      <c r="AM22" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13712,7 +14037,15 @@
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ22" s="9" t="inlineStr"/>
+      <c r="AQ22" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)
+■ 대응
+- 음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR22" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -13740,10 +14073,15 @@
           <t>딥페이크 기반 생체·본인확인 우회</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Deepfake-based biometric and identity verification bypass</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 얼굴 바꾸기로 은행 얼굴 인식·KYC를 통과해 계좌를 열거나 장악할 수 있음
+- 비대면 본인확인의 신뢰 기반이 무너져 금전 사기·명의 도용으로 직결됨</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -13758,7 +14096,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -13824,7 +14162,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB23" s="12" t="inlineStr">
+      <c r="AB23" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -13863,7 +14201,7 @@
       <c r="AL23" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="AM23" s="30" t="inlineStr">
+      <c r="AM23" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -13884,10 +14222,18 @@
 AC-2 Account Management</t>
         </is>
       </c>
-      <c r="AQ23" s="9" t="inlineStr"/>
+      <c r="AQ23" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)
+■ 대응
+- 강화된 라이브니스·다중 요소·문서 진위 검증과 위험 기반 추가 확인을 적용(NIST IA-2·AC-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉 · Group-IB 〈GoldPickaxe〉</t>
+        </is>
+      </c>
       <c r="AR23" s="9" t="inlineStr">
         <is>
-          <t>CNN·The Standard 〈홍콩 딥페이크 금융사기〉
+          <t>CNN 〈홍콩 딥페이크 금융사기〉
 Group-IB 〈GoldPickaxe〉</t>
         </is>
       </c>
@@ -13913,10 +14259,15 @@
           <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI lures, ClickFix and crafted links to induce execution</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI가 만든 미끼 페이지·링크로 사람 또는 컴퓨터 사용 에이전트가 악성 명령을 실행하도록 유도할 수 있음
+- 사람과 AI 에이전트를 함께 속이는 신규 경로라 기존 사용자 교육만으로는 막기 어려움</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -13931,7 +14282,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -14003,7 +14354,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB24" s="14" t="inlineStr">
+      <c r="AB24" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -14042,7 +14393,7 @@
       <c r="AL24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM24" s="29" t="inlineStr">
+      <c r="AM24" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -14060,7 +14411,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ24" s="9" t="inlineStr"/>
+      <c r="AQ24" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)
+- 참고: Embrace The Red 〈AI ClickFix〉</t>
+        </is>
+      </c>
       <c r="AR24" s="9" t="inlineStr">
         <is>
           <t>Embrace The Red 〈AI ClickFix〉</t>
@@ -14088,10 +14447,15 @@
           <t>단일 자율 공격 에이전트 실행</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Single autonomous attack agent execution</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>단일 자율 에이전트가 정찰~실행을 사람 속도 밖에서 수행</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈옥 모델·공격 프레임워크로 하나의 자율 에이전트가 정찰부터 실행까지 대부분을 스스로 수행하게 할 수 있음
+- 사람이 대응하기 어려운 속도·규모로 다수 조직을 동시에 침해해 피해 범위를 가늠하기 어려움</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -14106,7 +14470,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -14181,7 +14545,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB25" s="12" t="inlineStr">
+      <c r="AB25" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14220,7 +14584,7 @@
       <c r="AL25" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="AM25" s="30" t="inlineStr">
+      <c r="AM25" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14243,7 +14607,17 @@
 CA-7 Continuous Monitoring</t>
         </is>
       </c>
-      <c r="AQ25" s="9" t="inlineStr"/>
+      <c r="AQ25" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사람 속도를 넘는 반복·연쇄 행위 시퀀스와 비정상 세션 속도를 행위 기반으로 탐지(NIST SI-4·AU-6)
+- 전 단계를 가로지르는 상관 이벤트를 지속 모니터링(NIST CA-7)
+■ 대응
+- AI 속도 공격을 전제한 탐지·대응 자동화와 대응 속도 단축, AI 제공자 오남용 탐지 연계(NIST SI-4)
+- 지속 모니터링·사후 감사로 자율 공격 흔적을 추적(NIST AU-6·CA-7)
+- 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
+        </is>
+      </c>
       <c r="AR25" s="9" t="inlineStr">
         <is>
           <t>Anthropic 〈GTG-1002〉
@@ -14273,10 +14647,15 @@
           <t>다중 에이전트 공격 조율</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Multi-agent attack orchestration</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 상위 오케스트레이터가 다수 하위 에이전트를 조율해 공격 웨이브를 병렬 수행하게 할 수 있음
+- 공격 규모가 사람 조직의 한계를 벗어나 넓은 표적을 짧은 시간에 침해함</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -14291,7 +14670,7 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -14359,7 +14738,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB26" s="12" t="inlineStr">
+      <c r="AB26" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14398,7 +14777,7 @@
       <c r="AL26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="AM26" s="30" t="inlineStr">
+      <c r="AM26" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14420,7 +14799,15 @@
 CA-7 Continuous Monitoring</t>
         </is>
       </c>
-      <c r="AQ26" s="9" t="inlineStr"/>
+      <c r="AQ26" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)
+■ 대응
+- 교차 표적 상관 분석과 대응 자동화로 병렬 웨이브에 대응하고 사후 감사로 조율 구조를 추적(NIST SI-4·AU-6)
+- 참고: Dream Research 〈Multi-Agent Framework〉 · Anthropic 〈GTG-1002〉</t>
+        </is>
+      </c>
       <c r="AR26" s="9" t="inlineStr">
         <is>
           <t>Dream Research 〈Multi-Agent Framework〉
@@ -14449,10 +14836,15 @@
           <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of victim-side AI CLIs and local agents</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 피해 단말에 정상 설치된 AI CLI를 위험 옵션으로 실행해 비밀 탐색·반출에 악용할 수 있음
+- 정상 도구가 공격 실행 엔진이 되어 신뢰된 바이너리라 기존 탐지가 걸러내기 어려움</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -14467,7 +14859,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -14546,7 +14938,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB27" s="12" t="inlineStr">
+      <c r="AB27" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14585,7 +14977,7 @@
       <c r="AL27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AM27" s="30" t="inlineStr">
+      <c r="AM27" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14607,7 +14999,15 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AQ27" s="9" t="inlineStr"/>
+      <c r="AQ27" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- AI 개발 도구의 실행 권한·위험 옵션을 최소 권한·허용 목록으로 제한(NIST AC-6·CM-7)
+- 참고: Wiz 〈s1ngularity〉</t>
+        </is>
+      </c>
       <c r="AR27" s="9" t="inlineStr">
         <is>
           <t>Wiz 〈s1ngularity〉</t>
@@ -14635,10 +15035,15 @@
           <t>AI 개발 도구 신뢰·설정 악용</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of trust and configuration in AI development tools</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 코딩 에이전트의 폭넓은 실행 권한과 설정 신뢰를 악용해 공격 수행을 맡길 수 있음
+- AI 도구의 권한이 공격자 손에 들어가면 파괴·공급망 주입 같은 행위가 자동화됨</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -14653,7 +15058,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -14732,7 +15137,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB28" s="12" t="inlineStr">
+      <c r="AB28" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14771,7 +15176,7 @@
       <c r="AL28" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="AM28" s="30" t="inlineStr">
+      <c r="AM28" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14793,7 +15198,15 @@
 SA-15 Development Process, Standards, and Tools</t>
         </is>
       </c>
-      <c r="AQ28" s="9" t="inlineStr"/>
+      <c r="AQ28" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)
+■ 대응
+- AI 도구의 권한·승인 경계를 최소화하고 개발 파이프라인 변경을 검증(NIST AC-6·SA-15)
+- 참고: Ctrl-Alt-Intel 〈BuddyBoss〉</t>
+        </is>
+      </c>
       <c r="AR28" s="9" t="inlineStr">
         <is>
           <t>Ctrl-Alt-Intel 〈BuddyBoss〉</t>
@@ -14821,10 +15234,15 @@
           <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous agent mass-exploitation of CI/CD and workflows</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 보이는 계정이 공개 저장소의 워크플로 결함을 자동 탐색·악용해 다수 저장소에서 코드 실행·토큰 탈취를 할 수 있음
+- 공급망 전반을 자동·대량으로 침해하고 탈취 자격증명이 연쇄 침해의 출발점이 됨</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -14839,7 +15257,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -14914,7 +15332,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB29" s="12" t="inlineStr">
+      <c r="AB29" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -14953,7 +15371,7 @@
       <c r="AL29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM29" s="30" t="inlineStr">
+      <c r="AM29" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -14975,7 +15393,15 @@
 SA-15 Development Process, Standards, and Tools</t>
         </is>
       </c>
-      <c r="AQ29" s="9" t="inlineStr"/>
+      <c r="AQ29" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)
+■ 대응
+- 워크플로 트리거·권한을 최소화하고(pull_request_target 등) 파이프라인 변경을 검증(NIST CM-7·SA-15)
+- 참고: StepSecurity 〈hackerbot-claw〉</t>
+        </is>
+      </c>
       <c r="AR29" s="9" t="inlineStr">
         <is>
           <t>StepSecurity 〈hackerbot-claw〉</t>
@@ -15003,10 +15429,15 @@
           <t>AI 가속 자격증명 탈취·내부 확산</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated credential theft and lateral movement</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>AI 가속 자격증명 탈취·측면 이동으로 클라우드 전반 급속 장악</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 보조로 자격증명 탈취·측면 이동을 가속해 개발 환경 침해에서 클라우드 전반 장악까지 짧은 시간에 이를 수 있음
+- 확산 속도가 사람 대응 주기를 앞질러 선제 차단이 어려움</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -15021,7 +15452,7 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -15102,7 +15533,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB30" s="12" t="inlineStr">
+      <c r="AB30" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -15141,7 +15572,7 @@
       <c r="AL30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AM30" s="30" t="inlineStr">
+      <c r="AM30" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15163,7 +15594,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ30" s="9" t="inlineStr"/>
+      <c r="AQ30" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)
+■ 대응
+- 최소 권한·단기 자격증명·이상 접근 차단으로 확산 속도를 늦춤(NIST AC-2·AC-6)
+- 참고: Sygnia 〈AI-Assisted Cloud Attack〉</t>
+        </is>
+      </c>
       <c r="AR30" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉
@@ -15192,10 +15631,15 @@
           <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Covert C2 via AI service APIs and web interfaces</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 AI 서비스의 API·웹 인터페이스에 C2를 숨겨 데이터 반출·명령 수신의 양방향 채널을 만들 수 있음
+- 정상 서비스 트래픽이라 경계·egress 통제가 걸러내기 어려워 탐지가 지연됨</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -15210,7 +15654,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -15286,7 +15730,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB31" s="13" t="inlineStr">
+      <c r="AB31" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15325,7 +15769,7 @@
       <c r="AL31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="AM31" s="30" t="inlineStr">
+      <c r="AM31" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15348,7 +15792,15 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AQ31" s="9" t="inlineStr"/>
+      <c r="AQ31" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)
+■ 대응
+- AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)
+- 참고: Check Point 〈AI in the Middle〉</t>
+        </is>
+      </c>
       <c r="AR31" s="9" t="inlineStr">
         <is>
           <t>Check Point 〈AI in the Middle〉</t>
@@ -15376,10 +15828,15 @@
           <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Malware generating commands dynamically from AI at runtime</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성코드가 실행 중 LLM API에 질의해 명령을 매번 새로 생성하게 만들 수 있음
+- 고정 페이로드·시그니처가 없어 정적 분석·시그니처 탐지가 무력화됨</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -15394,7 +15851,7 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -15465,7 +15922,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB32" s="13" t="inlineStr">
+      <c r="AB32" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -15504,7 +15961,7 @@
       <c r="AL32" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="AM32" s="30" t="inlineStr">
+      <c r="AM32" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15526,7 +15983,15 @@
 AU-6 Audit Record Review, Analysis, and Reporting</t>
         </is>
       </c>
-      <c r="AQ32" s="9" t="inlineStr"/>
+      <c r="AQ32" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)
+■ 대응
+- AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)
+- 참고: The Hacker News 〈LAMEHUG〉</t>
+        </is>
+      </c>
       <c r="AR32" s="9" t="inlineStr">
         <is>
           <t>The Hacker News 〈LAMEHUG〉</t>
@@ -15554,10 +16019,15 @@
           <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven defense evasion and obfuscation</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 페이로드를 자동 변형·난독화하거나 적대적 입력으로 ML 기반 탐지기를 회피할 수 있음
+- 시그니처·정적 탐지를 체계적으로 우회하지만 행위 기반 탐지로 일부 포착이 가능함</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -15572,7 +16042,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -15645,7 +16115,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB33" s="14" t="inlineStr">
+      <c r="AB33" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -15684,7 +16154,7 @@
       <c r="AL33" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="AM33" s="29" t="inlineStr">
+      <c r="AM33" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -15698,7 +16168,15 @@
 SI-7 Software, Firmware, and Information Integrity</t>
         </is>
       </c>
-      <c r="AQ33" s="9" t="inlineStr"/>
+      <c r="AQ33" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR33" s="9" t="inlineStr">
         <is>
           <t>HiddenLayer 〈2026 AI Threat Landscape〉</t>
@@ -15726,10 +16204,15 @@
           <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Hidden-instruction injection into AI coding tool rules and configs</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 규칙 파일에 보이지 않는 유니코드로 지시를 숨겨 AI가 생성 코드에 백도어를 넣게 하거나 에이전트에 파괴 지시를 주입할 수 있음
+- 사람 리뷰가 알아채기 어려운 은닉 경로라 공급망을 통해 널리 퍼질 수 있음</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -15744,7 +16227,7 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -15823,7 +16306,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB34" s="14" t="inlineStr">
+      <c r="AB34" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -15862,7 +16345,7 @@
       <c r="AL34" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="AM34" s="30" t="inlineStr">
+      <c r="AM34" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -15881,7 +16364,15 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AQ34" s="9" t="inlineStr"/>
+      <c r="AQ34" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)
+■ 대응
+- 규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)
+- 참고: Pillar Security 〈Rules File Backdoor〉</t>
+        </is>
+      </c>
       <c r="AR34" s="9" t="inlineStr">
         <is>
           <t>Pillar Security 〈Rules File Backdoor〉</t>
@@ -15909,10 +16400,15 @@
           <t>딥페이크·AI 사칭 기반 금전 사기</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial fraud via deepfake and AI impersonation</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 딥페이크·AI 사칭으로 승인권자를 속여 대규모 부정 송금을 성사시킬 수 있음
+- 한 번의 성공으로 조직에 큰 금전 피해가 발생함</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -15927,7 +16423,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -15994,7 +16490,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB35" s="13" t="inlineStr">
+      <c r="AB35" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -16033,7 +16529,7 @@
       <c r="AL35" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="AM35" s="30" t="inlineStr">
+      <c r="AM35" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16054,10 +16550,18 @@
 IA-2 Identification and Authentication (Organizational Users)</t>
         </is>
       </c>
-      <c r="AQ35" s="9" t="inlineStr"/>
+      <c r="AQ35" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고액·비정상 송금 요청과 사칭 징후를 결제·승인 흐름에서 모니터링(NIST IA-2)
+■ 대응
+- 고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
+        </is>
+      </c>
       <c r="AR35" s="9" t="inlineStr">
         <is>
-          <t>CNN·The Standard 〈홍콩 딥페이크 금융사기〉</t>
+          <t>CNN 〈홍콩 딥페이크 금융사기〉</t>
         </is>
       </c>
     </row>
@@ -16082,10 +16586,15 @@
           <t>AI 가속 대규모 데이터 탈취·반출</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated large-scale data theft and exfiltration</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 자동 수집·반출로 대규모 데이터 유출</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 침해 환경에서 자율 에이전트로 민감 데이터를 자동 수집·분류·반출해 대규모 유출을 빠르게 완료할 수 있음
+- 수집-반출이 자동화돼 사람 대응 전에 유출이 끝나 피해 범위가 커짐</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -16100,7 +16609,7 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -16177,7 +16686,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="AB36" s="12" t="inlineStr">
+      <c r="AB36" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -16216,7 +16725,7 @@
       <c r="AL36" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="AM36" s="30" t="inlineStr">
+      <c r="AM36" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16238,7 +16747,15 @@
 SC-7 Boundary Protection</t>
         </is>
       </c>
-      <c r="AQ36" s="9" t="inlineStr"/>
+      <c r="AQ36" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)
+■ 대응
+- 데이터 접근 최소화·DLP·egress 통제로 자동 반출을 차단하고 조기 경보(NIST SC-7·SI-4)
+- 참고: Dream Research 〈Multi-Agent Framework〉</t>
+        </is>
+      </c>
       <c r="AR36" s="9" t="inlineStr">
         <is>
           <t>Dream Research 〈Multi-Agent Framework〉</t>
@@ -16266,10 +16783,15 @@
           <t>AI 인프라 악용 크립토재킹</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cryptojacking via abused AI infrastructure</t>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>노출·오설정 AI 인프라 악용 크립토재킹으로 자원 탈취</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 노출·오설정된 AI 인프라에 AI 생성 페이로드를 올려 크립토마이닝에 악용할 수 있음
+- 자원·비용 피해가 크나 데이터 유출·파괴보다는 영향이 제한적임</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -16284,7 +16806,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -16362,7 +16884,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB37" s="13" t="inlineStr">
+      <c r="AB37" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -16401,7 +16923,7 @@
       <c r="AL37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="AM37" s="30" t="inlineStr">
+      <c r="AM37" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16423,7 +16945,15 @@
 CM-7 Least Functionality</t>
         </is>
       </c>
-      <c r="AQ37" s="9" t="inlineStr"/>
+      <c r="AQ37" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 인프라의 비정상 자원 사용·외부 노출·무인증 접근을 모니터링(NIST SI-4·CM-7)
+■ 대응
+- AI 인프라 인증·접근 통제와 노출 최소화·최소 권한으로 자원 탈취를 차단(NIST AC-6·CM-7)
+- 참고: Oligo 〈ShadowRay 2.0〉</t>
+        </is>
+      </c>
       <c r="AR37" s="9" t="inlineStr">
         <is>
           <t>Oligo 〈ShadowRay 2.0〉</t>
@@ -16451,10 +16981,15 @@
           <t>LLMjacking·AI 과금 폭탄</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) LLMjacking and AI cost-harvesting</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>탈취 자격증명으로 관리형 LLM·GPU 무단 사용(LLMjacking)</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 자격증명으로 피해자 계정의 관리형 LLM·GPU 자원을 무단 사용할 수 있음
+- 과금 피해와 함께 추가 공격 역량 확보로 이어짐</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -16469,7 +17004,7 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -16548,7 +17083,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB38" s="14" t="inlineStr">
+      <c r="AB38" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -16587,7 +17122,7 @@
       <c r="AL38" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="AM38" s="30" t="inlineStr">
+      <c r="AM38" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -16609,7 +17144,15 @@
 SI-4 System Monitoring</t>
         </is>
       </c>
-      <c r="AQ38" s="9" t="inlineStr"/>
+      <c r="AQ38" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)
+■ 대응
+- 자격증명 최소 권한·단기화와 사용량 이상 탐지·한도로 무단 사용을 차단(NIST AC-2·AC-6)
+- 참고: Sygnia 〈AI-Assisted Cloud Attack〉</t>
+        </is>
+      </c>
       <c r="AR38" s="9" t="inlineStr">
         <is>
           <t>Sygnia 〈AI-Assisted Cloud Attack〉</t>
@@ -16637,10 +17180,15 @@
           <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scaling and mass-production of AI-enabled attacks</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 공격당 비용을 낮춰 캠페인을 대량·병렬로 벌여 전체 공격량과 빈도를 끌어올릴 수 있음
+- 개별 피해보다 공격 생태계 전반의 규모·속도가 커지는 것이 핵심 위협임</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -16655,7 +17203,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>문구 미작성</t>
+          <t>분석가 작성</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -16717,7 +17265,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="AB39" s="14" t="inlineStr">
+      <c r="AB39" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -16756,7 +17304,7 @@
       <c r="AL39" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="AM39" s="28" t="inlineStr">
+      <c r="AM39" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -16775,7 +17323,15 @@
 PM-16 Threat Awareness Program</t>
         </is>
       </c>
-      <c r="AQ39" s="9" t="inlineStr"/>
+      <c r="AQ39" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)
+■ 대응
+- 탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)
+- 참고: CrowdStrike 〈Agentic AI Campaigns〉 · HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
       <c r="AR39" s="9" t="inlineStr">
         <is>
           <t>CrowdStrike 〈Agentic AI Campaigns〉
@@ -16954,10 +17510,15 @@
           <t>AI 기반 공개정보 수집·인물 프로파일링</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven OSINT and target profiling</t>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공개정보를 대규모 수집·요약해 핵심 인력·약점 표적화</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LLM으로 업무용 SNS·논문·코드 저장소·보도자료를 대량 수집·요약해 핵심 인력과 그 관계·약점을 빠르게 추려낼 수 있음
+- 열람 자체는 합법이라 막기 어렵고, AI가 사람보다 빠르게 표적 명단을 만들어 후속 사회공학·침투의 발판이 됨</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -16995,7 +17556,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17003,7 +17564,7 @@
       <c r="O3" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="P3" s="28" t="inlineStr">
+      <c r="P3" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -17014,7 +17575,17 @@
       <c r="R3" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="S3" s="9" t="inlineStr"/>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사·임직원 대상 공개정보 노출과 비정상 수집 정황(대량 조회·스크레이핑)을 위협 인텔리전스로 점검(NIST PM-16·SI-4)
+- 특정 부서·인력에 몰리는 외부 접촉·채용 제안의 반복 출처를 식별
+■ 대응
+- 핵심 인력·과제의 공개 노출 범위를 정하고 프로필·발표·채용 공고의 민감 정보를 최소화(NIST PM-16)
+- 공개정보가 AI 정찰·표적 선정에 쓰이는 방식과 의심 접근 신고 경로를 교육(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -17037,10 +17608,15 @@
           <t>AI 기반 표적 환경·관계 분석</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted analysis of target environment and relationships</t>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>AI로 조직 구조·거래 관계를 엮어 사칭 시나리오·표적 우선순위 작성</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 수집한 조직도·거래 관계·내부 용어를 AI로 상관분석해 설득력 있는 사칭 시나리오와 표적 우선순위를 만들 수 있음
+- 외부에서 보이는 관계만으로도 맥락이 재구성되어, 피해는 뒤따르는 사회공학·침투 단계에서 커짐</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -17078,7 +17654,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17086,7 +17662,7 @@
       <c r="O4" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="P4" s="29" t="inlineStr">
+      <c r="P4" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -17097,7 +17673,17 @@
       <c r="R4" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="S4" s="9" t="inlineStr"/>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공개된 조직·거래 정보의 노출 범위와 사칭에 쓰일 수 있는 맥락을 주기적으로 점검(NIST PM-16·SI-4)
+- 경영진·재무·조달 등 고가치 역할에 대한 외부 정보 수집 정황을 모니터링
+■ 대응
+- 조직 구조·거래 관계의 불필요한 공개를 줄이고 고위험 역할의 공개 노출을 관리(NIST PM-16)
+- 사칭 시나리오를 전제한 다채널 확인 절차를 고위험 승인에 적용(NIST SI-4)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -17120,10 +17706,15 @@
           <t>AI 에이전트의 노출 자산·공격면 자동 식별</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Agent-driven identification of exposed assets and attack surface</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트가 노출 자산·공격면을 자동 열거해 진입점 식별</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 에이전트로 인터넷 스캔·FOFA 조회를 자동화해 노출된 서비스·관리 인터페이스를 사람보다 빠르게 열거할 수 있음
+- 공격 가능 진입점 목록이 자동 생성돼 정찰-침투 간격이 짧아지고, 탐지·패치 전 선제 악용 위험이 커짐</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -17161,7 +17752,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17169,7 +17760,7 @@
       <c r="O5" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17180,7 +17771,17 @@
       <c r="R5" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="S5" s="9" t="inlineStr"/>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 외부 노출 자산을 지속 식별하고 비정상적으로 빠른 열거·탐침 패턴을 모니터링(NIST RA-5·SI-4)
+- 관리 인터페이스·디버그 엔드포인트의 외부 노출을 상시 점검
+■ 대응
+- 공격면을 줄이고 관리 인터페이스를 경계 밖에 노출하지 않음(NIST SC-7)
+- 노출 자산 인벤토리와 신속 패치로 자율 열거-악용 간격을 좁힘(NIST RA-5)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -17203,10 +17804,15 @@
           <t>AI 기반 취약점 정보·공개 PoC 자동 수집·분류</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven collection and triage of vulnerability intel and public PoCs</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>AI로 최신 CVE·공개 PoC를 자동 수집·분류해 악용 준비 가속</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 공개 취약점 정보와 PoC를 자동 수집·분류해 공격에 쓸 형태로 빠르게 정리할 수 있음
+- 공개 즉시 악용되는 빠른 n-day를 가속해, 패치 전 노출 구간에서 피해 위험이 커짐</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -17244,7 +17850,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17252,7 +17858,7 @@
       <c r="O6" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17263,7 +17869,17 @@
       <c r="R6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S6" s="9" t="inlineStr"/>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사 자산의 공개 취약점·PoC 공개 동향을 신속 수집해 노출 여부를 대조(NIST RA-5)
+- 공개 직후 집중되는 탐침·악용 시도를 모니터링
+■ 대응
+- 공개 취약점의 신속 패치·완화를 우선순위화해 n-day 노출 구간을 좁힘(NIST RA-5)
+- 위협 인텔로 악용 가능성이 높은 취약점을 선별 대응(NIST PM-16)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -17286,10 +17902,15 @@
           <t>다크 LLM·탈옥 모델 확보</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of dark LLMs and jailbroken models</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>가드레일 없는 다크·탈옥 LLM 확보로 공세 역량 진입장벽 하락</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 지하 시장에서 가드레일이 제거된 공세 특화·탈옥 LLM을 구해 역량이 낮아도 피싱·악성코드 제작에 접근할 수 있음
+- 도구 확보 단계라 단독 피해는 없지만, 공격자 저변이 넓어져 후속 단계 전반의 빈도를 끌어올림</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -17327,7 +17948,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17335,7 +17956,7 @@
       <c r="O7" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="P7" s="28" t="inlineStr">
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -17346,7 +17967,15 @@
       <c r="R7" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="S7" s="9" t="inlineStr"/>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 지하 시장·공세 LLM 동향을 위협 인텔로 수집하고 자사 대상 악용 징후를 모니터링(NIST PM-16·SI-4)
+■ 대응
+- 공세 LLM이 만들어내는 산출물(피싱·악성코드)의 탐지·대응 역량을 강화해 역량 확보 자체보다 '사용 시점'을 막음(NIST SI-4)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -17369,10 +17998,15 @@
           <t>증류·파인튜닝으로 공세 역량 확보</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Distillation and fine-tuning to obtain offensive capability</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>증류·파인튜닝으로 가드레일 제거한 공세 모델 확보 정황</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 상용 모델을 증류·파인튜닝해 안전장치를 약화시킨 공세 모델을 만들려 시도할 수 있음
+- 아직 연구·시연 수준이라 직접 피해는 제한적이나, 성공 시 탐지가 어려운 전용 역량이 됨</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -17410,7 +18044,7 @@
           <t>하</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
@@ -17418,7 +18052,7 @@
       <c r="O8" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="P8" s="29" t="inlineStr">
+      <c r="P8" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -17429,7 +18063,15 @@
       <c r="R8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="S8" s="9" t="inlineStr"/>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 모델 가중치·데이터 유출과 비정상 대량 질의(증류 정황)를 자사 AI 자산에서 모니터링(NIST PM-16)
+■ 대응
+- 자사 모델·데이터의 유출·추출을 통제해 공세 파생 모델의 재료가 되지 않게 함(NIST PM-16)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -17452,10 +18094,15 @@
           <t>AI 기반 공격 도구·스크립트·셸 명령 생성</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated attack tools, scripts and shell commands</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>AI로 스캐너·셸 명령·탐침을 즉석 생성해 공격 준비 단축</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 스캐너·셸 명령·HTTP 탐침 같은 도구·스크립트를 즉석에서 생성해 공격 준비 시간을 줄일 수 있음
+- 단독 피해는 없으나 침투·실행 단계를 가속해 전체 공격 속도를 높임</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -17493,7 +18140,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17501,7 +18148,7 @@
       <c r="O9" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="P9" s="28" t="inlineStr">
+      <c r="P9" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -17512,7 +18159,15 @@
       <c r="R9" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="S9" s="9" t="inlineStr"/>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 실행 단계에서 생성형 도구의 산출물(비정형 스크립트·명령)을 행위 기반으로 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처가 아닌 행위·맥락 기반 탐지로 매번 달라지는 산출물에 대응하고 최소 권한을 적용(NIST SI-4·PM-16)
+- 참고: Unit 42 〈Hermes Agent〉</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -17535,10 +18190,15 @@
           <t>공격 인프라·AI 서비스 프록시 확보</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Acquisition of attack infrastructure and AI service proxies</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>탈취 계정·서버리스로 AI 서비스 익명 경유 공격 인프라 확보</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취·중계 계정이나 서버리스로 AI 서비스를 익명 경유하는 공격 인프라를 세워 출처·비용을 숨길 수 있음
+- 정상 서비스·인프라를 경유해 경계 통제가 걸러내기 어렵고, 후속 C2·대량 공격의 기반이 됨</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -17576,7 +18236,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17584,7 +18244,7 @@
       <c r="O10" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="P10" s="29" t="inlineStr">
+      <c r="P10" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -17595,7 +18255,15 @@
       <c r="R10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S10" s="9" t="inlineStr"/>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 서비스·클라우드로의 비정상 egress와 신규·일회성 계정·도메인 사용을 모니터링(NIST SC-7·SI-4)
+■ 대응
+- AI 서비스 egress 가시성을 확보하고 비인가 AI 트래픽·신규 인프라 접속을 통제(NIST SC-7)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -17618,10 +18286,15 @@
           <t>공세 AI 에이전트·공격 하네스 구축</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Building offensive AI agents and attack harnesses</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>스캐너·도구를 엮은 공세 AI 에이전트·공격 하네스 구축</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 스캐너·브라우저 자동화·침투 도구를 MCP 등으로 엮은 공격 프레임워크나 탈옥 모델 기반 자율 하네스를 구축할 수 있음
+- 한 번 만들면 사람 감독을 최소화한 반복·대규모 공격의 토대가 되어 피해 범위를 가늠하기 어려움</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -17659,7 +18332,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N11" s="12" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17667,7 +18340,7 @@
       <c r="O11" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="P11" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -17678,7 +18351,15 @@
       <c r="R11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="S11" s="9" t="inlineStr"/>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 에이전트 특유의 빠른·반복적 행위 시퀀스와 도구 연쇄 호출을 행위 기반으로 탐지(NIST SI-4·PM-16)
+■ 대응
+- AI 속도 공격을 전제한 탐지·대응 자동화와 AI 제공자 오남용 탐지 연계, 공격 하네스 구성 요소 차단(NIST SI-4·SA-11)
+- 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -17701,10 +18382,15 @@
           <t>AI 자율 취약점 발굴(버그 헌팅)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI vulnerability discovery (bug hunting)</t>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>AI 에이전트의 자율 취약점 발굴(미공개 취약점 자동 탐색)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 자율 AI 에이전트로 사람 개입 없이 미공개 취약점을 찾아내 대규모 표적에서 0-day를 양산할 수 있음
+- 같은 역량이 방어에도 쓰이지만, 공격자가 선점하면 패치 전 노출 구간에서 광범위한 악용으로 이어질 수 있음</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -17742,7 +18428,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N12" s="13" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -17750,7 +18436,7 @@
       <c r="O12" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="P12" s="28" t="inlineStr">
+      <c r="P12" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -17761,7 +18447,15 @@
       <c r="R12" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S12" s="9" t="inlineStr"/>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자사 자산에 대한 자동·대규모 취약점 탐색 정황과 비정상 접근 패턴을 모니터링(NIST RA-5)
+■ 대응
+- 자체 AI 보조 취약점 발굴·퍼징으로 공격자보다 먼저 찾고(NIST SA-11), 신속 패치·무결성 검증으로 노출 구간을 좁힘(NIST SI-7·RA-5)
+- 참고: The Record 〈Big Sleep〉 · AppSecSanta 〈AI Pentesting Agents 2026〉</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -17784,10 +18478,15 @@
           <t>AI 보조 코드 감사·퍼징</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-assisted code audit and fuzzing</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>AI 보조 코드 감사·퍼징으로 취약점 발견 속도 증폭</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 코드 리뷰·퍼징을 가속해 취약점 발견 속도를 높일 수 있음
+- 방어·공격 양용이라 단독 피해보다 발굴 단계를 증폭하며, 공급망 구성요소까지 넓게 겨냥될 수 있음</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -17825,7 +18524,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -17833,7 +18532,7 @@
       <c r="O13" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="P13" s="29" t="inlineStr">
+      <c r="P13" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -17844,7 +18543,15 @@
       <c r="R13" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="S13" s="9" t="inlineStr"/>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 의존성·자체 코드의 신규 취약점 공개와 악용 정황을 신속 대조(NIST RA-5)
+■ 대응
+- 개발 단계에 AI 보조 테스트를 통합해 선제 발견하고(NIST SA-11·SA-15), 취약 구성요소를 신속 교체(NIST RA-5)
+- 참고: AppSecSanta 〈AI Pentesting Agents 2026〉</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -17867,10 +18574,15 @@
           <t>AI 익스플로잇 자동 생성·개발</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous AI exploit generation and development</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>AI 익스플로잇 자동 생성으로 익스플로잇 개발 병목 제거</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 익스플로잇을 자동 생성·개발해, 공개 취약점을 사람 개입 없이 빠르게 무기화할 수 있음
+- 익스플로잇 개발 병목이 사라지면 공개 취약점이 즉시 악용돼 패치 전 노출 위험이 커짐</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -17908,7 +18620,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N14" s="13" t="inlineStr">
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -17916,7 +18628,7 @@
       <c r="O14" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="P14" s="28" t="inlineStr">
+      <c r="P14" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -17927,7 +18639,15 @@
       <c r="R14" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="S14" s="9" t="inlineStr"/>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 공개 직후 집중되는 익스플로잇 시도와 알려진 취약점의 비정상 악용을 모니터링(NIST RA-5)
+■ 대응
+- 신속 패치·가상 패치와 무결성 검증으로 즉시 무기화에 대응하고(NIST SI-7), 자체 익스플로잇 가능성 평가로 우선순위화(NIST SA-11·RA-5)
+- 참고: securityonline 〈GTIG AI 0-day〉</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -17950,10 +18670,15 @@
           <t>AI 생성·AI 연동 악성코드</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated and AI-integrated malware</t>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성·AI 연동 악성코드로 변종 양산·탐지 회피</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 생성형 AI로 악성코드를 개발·변형해 시그니처 기반 탐지를 빠르게 무력화할 수 있음
+- 변종 양산이 쉬워져 정적 분석·시그니처가 따라가기 어렵고, 금전·첩보 목적에 두루 쓰임</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -17991,7 +18716,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N15" s="12" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -17999,7 +18724,7 @@
       <c r="O15" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="30" t="inlineStr">
+      <c r="P15" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18010,7 +18735,15 @@
       <c r="R15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S15" s="9" t="inlineStr"/>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 시그니처가 아닌 행위·맥락 기반으로 변종 악성코드를 탐지하고 무결성 변화를 감시(NIST SI-3·SI-4·SI-7)
+■ 대응
+- 행위 기반 EDR·실행 통제로 변종에 대응하고(NIST SI-3), 무결성 검증으로 변조를 차단(NIST SI-7)
+- 참고: securityonline 〈GTIG AI 0-day〉</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -18033,10 +18766,15 @@
           <t>AI 생성 와이퍼·파괴 스크립트</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated wiper and destructive scripts</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 와이퍼·파괴 스크립트로 맞춤 파괴·복구 방해</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 LLM으로 와이퍼·파괴 스크립트를 맞춤 생성·변형해 파괴형 공격을 빠르게 전개할 수 있음
+- 맞춤 생성으로 탐지·복구가 어려워지고, 기반시설 대상 시 운영·안전에 큰 피해가 날 수 있음</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -18074,7 +18812,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N16" s="13" t="inlineStr">
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -18082,7 +18820,7 @@
       <c r="O16" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="P16" s="30" t="inlineStr">
+      <c r="P16" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18093,7 +18831,15 @@
       <c r="R16" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S16" s="9" t="inlineStr"/>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량 파일 변경·삭제와 파괴형 실행 행위를 조기 탐지하고 백업 무결성을 감시(NIST SI-3·SI-7)
+■ 대응
+- 행위 기반 탐지·실행 통제와 오프라인·불변 백업으로 복구력을 확보(NIST SI-7·CP-9)
+- 참고: CERT Polska 〈Energy Report 2025〉</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -18116,10 +18862,15 @@
           <t>AI 생성 대량 피싱·미끼</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-generated mass phishing and lures</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>AI 생성 대량 피싱·미끼로 기존 피싱 탐지 단서 무력화</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 문법·맥락이 자연스러운 피싱 미끼를 대량 생성해, 오탈자·어색함에 기대던 기존 탐지를 무력화할 수 있음
+- 품질·규모가 함께 올라가 더 많은 표적이 속고, 피해는 계정 탈취·BEC로 이어짐</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -18157,7 +18908,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18165,7 +18916,7 @@
       <c r="O17" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="P17" s="30" t="inlineStr">
+      <c r="P17" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18176,7 +18927,16 @@
       <c r="R17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="S17" s="9" t="inlineStr"/>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 발신 평판·행위·링크 분석 등 콘텐츠 품질에 덜 의존하는 다중 신호로 피싱을 탐지(NIST SI-4)
+- 디바이스 코드·OAuth 동의 등 비정상 인증 흐름을 모니터링(NIST SC-7)
+■ 대응
+- 피싱 내성 MFA·조건부 접근과 사용자 신고·교육으로 대량 미끼에 대응(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -18199,10 +18959,15 @@
           <t>AI 기반 표적 스피어피싱·BEC</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven targeted spear-phishing and BEC</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>AI로 맥락 맞춘 표적 스피어피싱·BEC로 특정 인물 공략</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 수집한 표적 정보를 AI로 엮어 맥락에 맞는 사칭 메시지를 만들어 특정 인물을 노릴 수 있음
+- 개인화 품질이 높아 의심을 사기 어렵고, 송금·자격증명 탈취로 직결될 수 있음</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -18240,7 +19005,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18248,7 +19013,7 @@
       <c r="O18" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="P18" s="28" t="inlineStr">
+      <c r="P18" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -18259,7 +19024,15 @@
       <c r="R18" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S18" s="9" t="inlineStr"/>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고위험 역할 대상 메시지의 이상 징후(발신 경로·요청 맥락)와 비정상 송금·승인 요청을 모니터링(NIST SI-4)
+■ 대응
+- 고액·고위험 요청에 다채널 확인과 역할 기반 교육을 적용(NIST AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -18282,10 +19055,15 @@
           <t>영상 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Video deepfake impersonation</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>영상 딥페이크 사칭으로 화상회의·면접 신뢰 악용</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 공개 영상으로 만든 영상 딥페이크로 경영진·동료를 사칭해 화상회의·면접에서 지시·신뢰를 얻을 수 있음
+- 사람의 시각 신뢰를 직접 무너뜨려 고액 송금·내부 접근 같은 큰 피해로 직결됨</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -18323,7 +19101,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N19" s="12" t="inlineStr">
+      <c r="N19" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18331,7 +19109,7 @@
       <c r="O19" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="P19" s="30" t="inlineStr">
+      <c r="P19" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18342,7 +19120,15 @@
       <c r="R19" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S19" s="9" t="inlineStr"/>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고액·고위험 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검(NIST IA-2)
+■ 대응
+- 고위험 요청에 다채널·사전 등록 경로 확인을 의무화하고 사용자 교육(NIST AT-2(3)·IA-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -18365,10 +19151,15 @@
           <t>음성 딥페이크 사칭</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Voice deepfake impersonation</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>음성 딥페이크 사칭으로 전화 본인확인·헬프데스크 우회</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 직원·임원 목소리를 딥페이크로 흉내 내 전화 본인확인·헬프데스크 절차를 우회하고 추가 인증·승인을 받아낼 수 있음
+- 음성 신뢰에 기대던 절차가 뚫려 계정 등록·접근 확대로 이어짐</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -18406,7 +19197,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18414,7 +19205,7 @@
       <c r="O20" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="P20" s="30" t="inlineStr">
+      <c r="P20" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18425,7 +19216,15 @@
       <c r="R20" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S20" s="9" t="inlineStr"/>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 헬프데스크·계정 복구 요청의 음성 사칭 징후와 비정상 MFA 등록을 점검(NIST IA-2)
+■ 대응
+- 음성에 의존하지 않는 본인확인(콜백·사전 등록·피싱 내성 MFA)과 헬프데스크 절차 강화(NIST IA-2·AT-2(3))
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -18448,10 +19247,15 @@
           <t>딥페이크 기반 생체·본인확인 우회</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Deepfake-based biometric and identity verification bypass</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크로 생체·비대면 본인확인(KYC) 우회해 계정 장악</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 얼굴 바꾸기로 은행 얼굴 인식·KYC를 통과해 계좌를 열거나 장악할 수 있음
+- 비대면 본인확인의 신뢰 기반이 무너져 금전 사기·명의 도용으로 직결됨</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -18489,7 +19293,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N21" s="12" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18497,7 +19301,7 @@
       <c r="O21" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="P21" s="30" t="inlineStr">
+      <c r="P21" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18508,7 +19312,15 @@
       <c r="R21" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="S21" s="9" t="inlineStr"/>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설·접근 패턴을 모니터링(NIST IA-2·AC-2)
+■ 대응
+- 강화된 라이브니스·다중 요소·문서 진위 검증과 위험 기반 추가 확인을 적용(NIST IA-2·AC-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉 · Group-IB 〈GoldPickaxe〉</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -18531,10 +19343,15 @@
           <t>AI 미끼·ClickFix·크래프트 링크로 실행 유도</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI lures, ClickFix and crafted links to induce execution</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>AI 미끼·ClickFix·크래프트 링크로 사람·에이전트 실행 유도</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI가 만든 미끼 페이지·링크로 사람 또는 컴퓨터 사용 에이전트가 악성 명령을 실행하도록 유도할 수 있음
+- 사람과 AI 에이전트를 함께 속이는 신규 경로라 기존 사용자 교육만으로는 막기 어려움</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -18572,7 +19389,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="N22" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -18580,7 +19397,7 @@
       <c r="O22" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="P22" s="29" t="inlineStr">
+      <c r="P22" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -18591,7 +19408,15 @@
       <c r="R22" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="S22" s="9" t="inlineStr"/>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 에이전트·사용자의 미끼 실행 흐름(클립보드→터미널 등)과 의심 링크 접근을 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- 컴퓨터 사용 에이전트의 실행 권한·승인 경계를 두고 미끼 유형을 교육(NIST AT-2(3)·SI-4)
+- 참고: Embrace The Red 〈AI ClickFix〉</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -18614,10 +19439,15 @@
           <t>단일 자율 공격 에이전트 실행</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Single autonomous attack agent execution</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>단일 자율 에이전트가 정찰~실행을 사람 속도 밖에서 수행</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈옥 모델·공격 프레임워크로 하나의 자율 에이전트가 정찰부터 실행까지 대부분을 스스로 수행하게 할 수 있음
+- 사람이 대응하기 어려운 속도·규모로 다수 조직을 동시에 침해해 피해 범위를 가늠하기 어려움</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -18655,7 +19485,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N23" s="12" t="inlineStr">
+      <c r="N23" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18663,7 +19493,7 @@
       <c r="O23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P23" s="30" t="inlineStr">
+      <c r="P23" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18674,7 +19504,17 @@
       <c r="R23" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="S23" s="9" t="inlineStr"/>
+      <c r="S23" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 사람 속도를 넘는 반복·연쇄 행위 시퀀스와 비정상 세션 속도를 행위 기반으로 탐지(NIST SI-4·AU-6)
+- 전 단계를 가로지르는 상관 이벤트를 지속 모니터링(NIST CA-7)
+■ 대응
+- AI 속도 공격을 전제한 탐지·대응 자동화와 대응 속도 단축, AI 제공자 오남용 탐지 연계(NIST SI-4)
+- 지속 모니터링·사후 감사로 자율 공격 흔적을 추적(NIST AU-6·CA-7)
+- 참고: Anthropic 〈GTG-1002〉 · CrowdStrike 〈Agentic AI Campaigns〉</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -18697,10 +19537,15 @@
           <t>다중 에이전트 공격 조율</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Multi-agent attack orchestration</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>상위 오케스트레이터가 다중 하위 에이전트로 공격 웨이브 병렬화</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 상위 오케스트레이터가 다수 하위 에이전트를 조율해 공격 웨이브를 병렬 수행하게 할 수 있음
+- 공격 규모가 사람 조직의 한계를 벗어나 넓은 표적을 짧은 시간에 침해함</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -18738,7 +19583,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="N24" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18746,7 +19591,7 @@
       <c r="O24" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="P24" s="30" t="inlineStr">
+      <c r="P24" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18757,7 +19602,15 @@
       <c r="R24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="S24" s="9" t="inlineStr"/>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 동시다발 표적에 걸친 유사 패턴·상관 이벤트와 병렬 세션 급증을 탐지(NIST SI-4·CA-7)
+■ 대응
+- 교차 표적 상관 분석과 대응 자동화로 병렬 웨이브에 대응하고 사후 감사로 조율 구조를 추적(NIST SI-4·AU-6)
+- 참고: Dream Research 〈Multi-Agent Framework〉 · Anthropic 〈GTG-1002〉</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -18780,10 +19633,15 @@
           <t>피해 단말의 AI CLI·로컬 에이전트 악용</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of victim-side AI CLIs and local agents</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말에 설치된 AI CLI를 공격 실행 엔진으로 악용</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 피해 단말에 정상 설치된 AI CLI를 위험 옵션으로 실행해 비밀 탐색·반출에 악용할 수 있음
+- 정상 도구가 공격 실행 엔진이 되어 신뢰된 바이너리라 기존 탐지가 걸러내기 어려움</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -18821,7 +19679,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N25" s="12" t="inlineStr">
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18829,7 +19687,7 @@
       <c r="O25" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P25" s="30" t="inlineStr">
+      <c r="P25" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18840,7 +19698,15 @@
       <c r="R25" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="S25" s="9" t="inlineStr"/>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지(NIST SI-4)
+■ 대응
+- AI 개발 도구의 실행 권한·위험 옵션을 최소 권한·허용 목록으로 제한(NIST AC-6·CM-7)
+- 참고: Wiz 〈s1ngularity〉</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -18863,10 +19729,15 @@
           <t>AI 개발 도구 신뢰·설정 악용</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Abuse of trust and configuration in AI development tools</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>AI 개발 도구의 광범위 실행 권한·신뢰를 공격 수행에 악용</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 코딩 에이전트의 폭넓은 실행 권한과 설정 신뢰를 악용해 공격 수행을 맡길 수 있음
+- AI 도구의 권한이 공격자 손에 들어가면 파괴·공급망 주입 같은 행위가 자동화됨</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -18904,7 +19775,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
+      <c r="N26" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18912,7 +19783,7 @@
       <c r="O26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="P26" s="30" t="inlineStr">
+      <c r="P26" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -18923,7 +19794,15 @@
       <c r="R26" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="S26" s="9" t="inlineStr"/>
+      <c r="S26" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 개발 도구의 비정상 설정 변경·과도한 권한 사용·공급망 산출물 변조를 탐지(NIST SI-4·SA-15)
+■ 대응
+- AI 도구의 권한·승인 경계를 최소화하고 개발 파이프라인 변경을 검증(NIST AC-6·SA-15)
+- 참고: Ctrl-Alt-Intel 〈BuddyBoss〉</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -18946,10 +19825,15 @@
           <t>자율 에이전트의 CI/CD·워크플로 대량 악용</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Autonomous agent mass-exploitation of CI/CD and workflows</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트가 CI/CD·워크플로 결함을 자동·대량 악용</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 보이는 계정이 공개 저장소의 워크플로 결함을 자동 탐색·악용해 다수 저장소에서 코드 실행·토큰 탈취를 할 수 있음
+- 공급망 전반을 자동·대량으로 침해하고 탈취 자격증명이 연쇄 침해의 출발점이 됨</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -18987,7 +19871,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N27" s="12" t="inlineStr">
+      <c r="N27" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -18995,7 +19879,7 @@
       <c r="O27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P27" s="30" t="inlineStr">
+      <c r="P27" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19006,7 +19890,15 @@
       <c r="R27" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="S27" s="9" t="inlineStr"/>
+      <c r="S27" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지(NIST SI-4)
+■ 대응
+- 워크플로 트리거·권한을 최소화하고(pull_request_target 등) 파이프라인 변경을 검증(NIST CM-7·SA-15)
+- 참고: StepSecurity 〈hackerbot-claw〉</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -19029,10 +19921,15 @@
           <t>AI 가속 자격증명 탈취·내부 확산</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated credential theft and lateral movement</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>AI 가속 자격증명 탈취·측면 이동으로 클라우드 전반 급속 장악</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI 보조로 자격증명 탈취·측면 이동을 가속해 개발 환경 침해에서 클라우드 전반 장악까지 짧은 시간에 이를 수 있음
+- 확산 속도가 사람 대응 주기를 앞질러 선제 차단이 어려움</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -19070,7 +19967,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N28" s="12" t="inlineStr">
+      <c r="N28" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19078,7 +19975,7 @@
       <c r="O28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P28" s="30" t="inlineStr">
+      <c r="P28" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19089,7 +19986,15 @@
       <c r="R28" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="S28" s="9" t="inlineStr"/>
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 자격증명의 비정상 사용·급속한 권한 확대·측면 이동을 아이덴티티·클라우드 로그로 탐지(NIST AC-2·SI-4)
+■ 대응
+- 최소 권한·단기 자격증명·이상 접근 차단으로 확산 속도를 늦춤(NIST AC-2·AC-6)
+- 참고: Sygnia 〈AI-Assisted Cloud Attack〉</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -19112,10 +20017,15 @@
           <t>AI 서비스 API·웹 인터페이스 경유 은닉 C2</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Covert C2 via AI service APIs and web interfaces</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>정상 AI 서비스 트래픽에 숨긴 은닉 C2로 경계 통제 회피</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 정상 AI 서비스의 API·웹 인터페이스에 C2를 숨겨 데이터 반출·명령 수신의 양방향 채널을 만들 수 있음
+- 정상 서비스 트래픽이라 경계·egress 통제가 걸러내기 어려워 탐지가 지연됨</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -19153,7 +20063,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N29" s="13" t="inlineStr">
+      <c r="N29" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19161,7 +20071,7 @@
       <c r="O29" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="P29" s="30" t="inlineStr">
+      <c r="P29" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19172,7 +20082,15 @@
       <c r="R29" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="S29" s="9" t="inlineStr"/>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 서비스로의 비정상 egress 패턴·데이터량과 자동화된 세션을 모니터링(NIST SC-7·SI-4·AU-6)
+■ 대응
+- AI 서비스 egress 가시성·허용 목록으로 비인가 AI 트래픽을 통제(NIST SC-7)
+- 참고: Check Point 〈AI in the Middle〉</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -19195,10 +20113,15 @@
           <t>실행 중 AI 명령 동적 생성 악성코드</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Malware generating commands dynamically from AI at runtime</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>실행 중 LLM 질의로 명령을 매번 생성해 시그니처 탐지 무력화</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 악성코드가 실행 중 LLM API에 질의해 명령을 매번 새로 생성하게 만들 수 있음
+- 고정 페이로드·시그니처가 없어 정적 분석·시그니처 탐지가 무력화됨</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -19236,7 +20159,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N30" s="13" t="inlineStr">
+      <c r="N30" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19244,7 +20167,7 @@
       <c r="O30" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="P30" s="30" t="inlineStr">
+      <c r="P30" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19255,7 +20178,15 @@
       <c r="R30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="S30" s="9" t="inlineStr"/>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위·맥락 기반으로 탐지(NIST SI-3·SI-4·AU-6)
+■ 대응
+- AI 서비스 egress 통제와 행위 기반 실행 탐지로 동적 명령 생성에 대응(NIST SI-3·SI-4)
+- 참고: The Hacker News 〈LAMEHUG〉</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -19278,10 +20209,15 @@
           <t>AI 기반 방어 회피·난독화</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-driven defense evasion and obfuscation</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>AI로 페이로드 자동 변형·적대적 입력으로 ML 탐지 회피</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 페이로드를 자동 변형·난독화하거나 적대적 입력으로 ML 기반 탐지기를 회피할 수 있음
+- 시그니처·정적 탐지를 체계적으로 우회하지만 행위 기반 탐지로 일부 포착이 가능함</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -19319,7 +20255,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="N31" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19327,7 +20263,7 @@
       <c r="O31" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="P31" s="29" t="inlineStr">
+      <c r="P31" s="28" t="inlineStr">
         <is>
           <t>실증·공개 PoC</t>
         </is>
@@ -19338,7 +20274,15 @@
       <c r="R31" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="S31" s="9" t="inlineStr"/>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 행위·맥락 기반 탐지와 다중 엔진·이상 탐지로 변형·적대적 회피를 보완 탐지(NIST SI-3·SI-4)
+■ 대응
+- 시그니처 의존을 줄이고 행위 기반·무결성 검증을 강화, 탐지 모델에 적대적 견고성을 반영(NIST SI-4·SI-7)
+- 참고: HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -19361,10 +20305,15 @@
           <t>AI 코딩 도구 규칙·설정 숨은 지시 주입</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Hidden-instruction injection into AI coding tool rules and configs</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>AI 코딩 도구 규칙·설정에 숨은 지시 주입으로 은닉 백도어</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 규칙 파일에 보이지 않는 유니코드로 지시를 숨겨 AI가 생성 코드에 백도어를 넣게 하거나 에이전트에 파괴 지시를 주입할 수 있음
+- 사람 리뷰가 알아채기 어려운 은닉 경로라 공급망을 통해 널리 퍼질 수 있음</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -19402,7 +20351,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr">
+      <c r="N32" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19410,7 +20359,7 @@
       <c r="O32" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="P32" s="30" t="inlineStr">
+      <c r="P32" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19421,7 +20370,15 @@
       <c r="R32" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="S32" s="9" t="inlineStr"/>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 규칙·설정 파일의 비가시 문자·숨은 지시와 생성 코드의 의심 변경을 검사(NIST SI-7·SA-15)
+■ 대응
+- 규칙·설정 파일을 변경 통제·리뷰 대상에 포함하고 비가시 문자를 정규화·차단(NIST SA-15·CM-7)
+- 참고: Pillar Security 〈Rules File Backdoor〉</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -19444,10 +20401,15 @@
           <t>딥페이크·AI 사칭 기반 금전 사기</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Financial fraud via deepfake and AI impersonation</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크·AI 사칭으로 대규모 부정 송금 금전 사기 실현</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 딥페이크·AI 사칭으로 승인권자를 속여 대규모 부정 송금을 성사시킬 수 있음
+- 한 번의 성공으로 조직에 큰 금전 피해가 발생함</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -19485,7 +20447,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N33" s="13" t="inlineStr">
+      <c r="N33" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19493,7 +20455,7 @@
       <c r="O33" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="P33" s="30" t="inlineStr">
+      <c r="P33" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19504,7 +20466,15 @@
       <c r="R33" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="S33" s="9" t="inlineStr"/>
+      <c r="S33" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 고액·비정상 송금 요청과 사칭 징후를 결제·승인 흐름에서 모니터링(NIST IA-2)
+■ 대응
+- 고액 송금에 다채널·사전 등록 경로 확인과 역할 분리·한도를 적용(NIST AT-2(3)·IA-2)
+- 참고: CNN 〈홍콩 딥페이크 금융사기〉</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -19527,10 +20497,15 @@
           <t>AI 가속 대규모 데이터 탈취·반출</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) AI-accelerated large-scale data theft and exfiltration</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 자동 수집·반출로 대규모 데이터 유출</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 침해 환경에서 자율 에이전트로 민감 데이터를 자동 수집·분류·반출해 대규모 유출을 빠르게 완료할 수 있음
+- 수집-반출이 자동화돼 사람 대응 전에 유출이 끝나 피해 범위가 커짐</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -19568,7 +20543,7 @@
           <t>상</t>
         </is>
       </c>
-      <c r="N34" s="12" t="inlineStr">
+      <c r="N34" s="11" t="inlineStr">
         <is>
           <t>매우 높음</t>
         </is>
@@ -19576,7 +20551,7 @@
       <c r="O34" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P34" s="30" t="inlineStr">
+      <c r="P34" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19587,7 +20562,15 @@
       <c r="R34" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="S34" s="9" t="inlineStr"/>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 대량·자동화된 데이터 접근·반출 패턴과 비정상 egress를 모니터링(NIST SI-4·AU-6·SC-7)
+■ 대응
+- 데이터 접근 최소화·DLP·egress 통제로 자동 반출을 차단하고 조기 경보(NIST SC-7·SI-4)
+- 참고: Dream Research 〈Multi-Agent Framework〉</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -19610,10 +20593,15 @@
           <t>AI 인프라 악용 크립토재킹</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Cryptojacking via abused AI infrastructure</t>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>노출·오설정 AI 인프라 악용 크립토재킹으로 자원 탈취</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 노출·오설정된 AI 인프라에 AI 생성 페이로드를 올려 크립토마이닝에 악용할 수 있음
+- 자원·비용 피해가 크나 데이터 유출·파괴보다는 영향이 제한적임</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -19651,7 +20639,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N35" s="13" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
@@ -19659,7 +20647,7 @@
       <c r="O35" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="P35" s="30" t="inlineStr">
+      <c r="P35" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19670,7 +20658,15 @@
       <c r="R35" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="S35" s="9" t="inlineStr"/>
+      <c r="S35" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- AI 인프라의 비정상 자원 사용·외부 노출·무인증 접근을 모니터링(NIST SI-4·CM-7)
+■ 대응
+- AI 인프라 인증·접근 통제와 노출 최소화·최소 권한으로 자원 탈취를 차단(NIST AC-6·CM-7)
+- 참고: Oligo 〈ShadowRay 2.0〉</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -19693,10 +20689,15 @@
           <t>LLMjacking·AI 과금 폭탄</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) LLMjacking and AI cost-harvesting</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>탈취 자격증명으로 관리형 LLM·GPU 무단 사용(LLMjacking)</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 탈취한 자격증명으로 피해자 계정의 관리형 LLM·GPU 자원을 무단 사용할 수 있음
+- 과금 피해와 함께 추가 공격 역량 확보로 이어짐</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -19734,7 +20735,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N36" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19742,7 +20743,7 @@
       <c r="O36" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="P36" s="30" t="inlineStr">
+      <c r="P36" s="29" t="inlineStr">
         <is>
           <t>실제 사고 확인</t>
         </is>
@@ -19753,7 +20754,15 @@
       <c r="R36" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="S36" s="9" t="inlineStr"/>
+      <c r="S36" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 관리형 LLM·GPU의 비정상 사용량·과금 급증과 비정상 추론 호출을 모니터링(NIST AC-2·SI-4)
+■ 대응
+- 자격증명 최소 권한·단기화와 사용량 이상 탐지·한도로 무단 사용을 차단(NIST AC-2·AC-6)
+- 참고: Sygnia 〈AI-Assisted Cloud Attack〉</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -19776,10 +20785,15 @@
           <t>AI 활용 공격의 규모화·대량화</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>(문구 미작성) Scaling and mass-production of AI-enabled attacks</t>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>AI로 공격당 비용을 낮춰 캠페인 대량·병렬 규모화</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>- 공격자는 AI로 공격당 비용을 낮춰 캠페인을 대량·병렬로 벌여 전체 공격량과 빈도를 끌어올릴 수 있음
+- 개별 피해보다 공격 생태계 전반의 규모·속도가 커지는 것이 핵심 위협임</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -19817,7 +20831,7 @@
           <t>중</t>
         </is>
       </c>
-      <c r="N37" s="14" t="inlineStr">
+      <c r="N37" s="13" t="inlineStr">
         <is>
           <t>보통</t>
         </is>
@@ -19825,7 +20839,7 @@
       <c r="O37" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="P37" s="28" t="inlineStr">
+      <c r="P37" s="27" t="inlineStr">
         <is>
           <t>실사용 역량(성숙도)</t>
         </is>
@@ -19836,7 +20850,15 @@
       <c r="R37" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="S37" s="9" t="inlineStr"/>
+      <c r="S37" s="9" t="inlineStr">
+        <is>
+          <t>■ 탐지
+- 캠페인 규모·빈도 증가와 교차 표적 상관 지표를 지속 모니터링(NIST SI-4·CA-7)
+■ 대응
+- 탐지·대응 자동화로 대량 캠페인에 대응하고 위협 인텔로 우선순위화(NIST SI-4·PM-16)
+- 참고: CrowdStrike 〈Agentic AI Campaigns〉 · HiddenLayer 〈2026 AI Threat Landscape〉</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:S37"/>
@@ -20695,23 +21717,661 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오 — ③단계(data/scenarios.yaml)에서 작성</t>
+          <t>공격 체인 시나리오 8개 — 실제 사고 기반 공격 흐름(방어 관점)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>실제 사고를 공격 흐름으로 재구성해 한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 초크 포인트(가장 싸고 효과 큰 차단 지점)를 드러낼 예정</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>세부위협</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>행위(근거 사고)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>탐지·차단 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ASN-01</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>공세 AI 에이전트 프레임워크 구축 → 자율·다중 에이전트 첩보 작전</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>역량확보</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>AIA-RD-04</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>스캐너·브라우저 자동화·침투 도구를 MCP로 엮은 공격 프레임워크 구축(AII-008)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>AI 도구의 비정상 조합·자동화 설정과 제공자 측 오남용 신호를 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>ASN-01</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>공세 AI 에이전트 프레임워크 구축 → 자율·다중 에이전트 첩보 작전</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-01, AIA-AO-02</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>자율·다중 에이전트가 약 30개 조직을 표적해 공격의 80~90%를 수행(AII-008)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>사람 속도를 넘는 반복·연쇄 행위와 다수 표적에 걸친 상관 이벤트를 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>ASN-02</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>탈옥 모델 자율 하네스 → 노출 자산 열거·PoC 검색 → 자율 공격 시도</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>역량확보</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>AIA-RD-04</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>탈옥 모델을 자율 공세 운영자로 삼은 Hermes 하네스 구성(AII-027)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>탈옥 모델·자율 하네스의 비정상 트래픽·도구 호출 패턴을 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>ASN-02</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>탈옥 모델 자율 하네스 → 노출 자산 열거·PoC 검색 → 자율 공격 시도</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>정찰</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>AIA-RT-02, AIA-RT-03</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>FOFA로 노출된 Langflow·n8n을 스스로 열거하고 GitHub에서 최신 CVE PoC를 검색(AII-027)</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>비정상적으로 빠른 열거·탐침과 공개 자산 노출을 지속 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>ASN-02</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>탈옥 모델 자율 하네스 → 노출 자산 열거·PoC 검색 → 자율 공격 시도</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-01</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>노출 시스템을 자율로 공격 시도(접근 획득은 모두 실패)(AII-027)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>자동화된 연쇄 공격 시도와 세션 속도를 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>ASN-03</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말 AI CLI 악용 → 노출 클라우드 키 → 측면 이동으로 클라우드 장악</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-03.1</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말의 AI CLI를 위험 옵션으로 실행해 비밀을 탐색하고 비공개 저장소 5,500개 이상을 공개로 전환(AII-004)</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>AI CLI의 위험 옵션 실행·비정상 파일 탐색·외부 전송을 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>ASN-03</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>피해 단말 AI CLI 악용 → 노출 클라우드 키 → 측면 이동으로 클라우드 장악</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-03.1, AIA-AO-05</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>노출된 클라우드 키로 측면 이동하고 단말의 LLM 도구로 자격증명을 탐색해 72시간 안에 클라우드 전반 장악(AII-018)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>자격증명의 비정상 사용·급속한 권한 확대를 아이덴티티·클라우드 로그로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ASN-04</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 화상회의 사칭 → 승인권자 기만 → 대규모 부정 송금</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>초기침투</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-02.1</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>참석자 전원이 딥페이크인 화상회의로 CFO·동료를 사칭(AII-002)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>고액 지시의 출처를 영상 외 경로로 교차 확인하고 딥페이크·라이브니스 징후를 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ASN-04</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 화상회의 사칭 → 승인권자 기만 → 대규모 부정 송금</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IM-01</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>지시를 믿은 직원이 약 2,560만 달러를 부정 송금(AII-002)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>고액·비정상 송금 요청을 결제·승인 흐름에서 탐지하고 한도·역할 분리를 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ASN-05</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>AI 연동 악성코드 배포 → 실행 중 명령 동적 생성 → AI 서비스 은닉 C2</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>취약점발굴</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>AIA-VE-03.1</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>LLM 연동 악성코드를 사칭 메일로 배포(AII-007)</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>행위·맥락 기반으로 변종 악성코드를 탐지하고 메일 사칭을 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>ASN-05</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>AI 연동 악성코드 배포 → 실행 중 명령 동적 생성 → AI 서비스 은닉 C2</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>은닉C2</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>AIA-CC-02, AIA-CC-01</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>실행 중 LLM API 질의로 시스템 정보 수집·문서 검색 명령을 동적 생성하고 AI API로 은닉 통신(AII-007)</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>LLM API로의 비정상 egress와 동적 생성 명령 실행을 행위 기반으로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ASN-06</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 생체·본인확인(KYC) 우회 → 계좌 개설·장악</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>초기침투</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-03</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>AI 얼굴 바꾸기로 신분증 주인 얼굴로 바꿔 대출·계좌 개설 얼굴인식을 통과(AII-001)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>라이브니스·프레젠테이션 공격 탐지와 비정상 계좌 개설 패턴을 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>ASN-06</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>딥페이크 생체·본인확인(KYC) 우회 → 계좌 개설·장악</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>초기침투</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IA-03</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>트로이목마로 수집한 얼굴 데이터로 만든 딥페이크로 은행 생체 본인확인을 우회(AII-013)</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>위험 기반 추가 확인과 문서 진위·다중 요소 검증을 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>ASN-07</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 워크플로 대량 악용 → 토큰 탈취 → 연쇄 공급망 침해</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-04</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트가 공개 저장소의 워크플로 결함을 자동 탐색해 다수 저장소에서 코드 실행·토큰 탈취(AII-017)</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>워크플로에 대한 대량 자동 PR·비정상 실행과 토큰 사용을 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>ASN-07</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 워크플로 대량 악용 → 토큰 탈취 → 연쇄 공급망 침해</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-04</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>다수 저장소에 자동 악성 PR을 보내 pull_request_target을 악용(AII-020)</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>pull_request_target 등 위험 트리거의 비정상 호출을 모니터링</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>ASN-07</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>자율 에이전트의 워크플로 대량 악용 → 토큰 탈취 → 연쇄 공급망 침해</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-03.2, AIA-AO-04</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>AI 코딩 에이전트로 배포 파이프라인을 침해(AII-019)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>AI 개발 도구의 비정상 권한 사용·파이프라인 산출물 변조를 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>ASN-08</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>노출 자격증명 측면 이동 → 관리형 LLM·GPU 무단 사용 → AI 인프라 크립토재킹</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>자율실행</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>AIA-AO-05</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>공개 S3 버킷에 노출된 자격증명으로 초기 접근·측면 이동(AII-016)</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>자격증명 비정상 사용·권한 확대를 아이덴티티·클라우드 로그로 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>ASN-08</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>노출 자격증명 측면 이동 → 관리형 LLM·GPU 무단 사용 → AI 인프라 크립토재킹</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IM-03.2</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>피해자 계정의 Bedrock LLM과 GPU 인스턴스를 무단 사용(AII-016)</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>관리형 LLM·GPU의 사용량·과금 급증과 비정상 추론 호출을 탐지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ASN-08</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>노출 자격증명 측면 이동 → 관리형 LLM·GPU 무단 사용 → AI 인프라 크립토재킹</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>AIA-IM-03.1</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>인증 없이 노출된 AI 인프라에 AI 생성 페이로드로 크립토마이닝(AII-005)</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>AI 인프라의 비정상 자원 사용·무인증 접근을 모니터링</t>
         </is>
       </c>
     </row>

--- a/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v1.xlsx
+++ b/aiattack/output/통합_AI활용공격_보안위협_매트릭스_v1.xlsx
@@ -7179,7 +7179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7225,7 +7225,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -7235,22 +7235,22 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>통합</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>관점 문구(data/text/*.yaml)</t>
+          <t>통합본 뷰 Lv0 편입(scripts/build_integrated_view.py)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
+          <t>AI 활용 공격 매트릭스를 통합본 v4.1(요약 위협 237개)에 '뷰(view) Lv0'로 얹는 빌더·산출물 추가(D9). 렌즈라 기존 6개와 겹치므로 재수록 대신 연계만 하고 고유 위협 수에는 넣지 않음(이중계산 방지). 세부위협 35개의 연계(AI·CL·OT·SC·ID·PH)가 기존 237개 중 29개를 닿음(교차 54건). 산출물: integrated/output/통합_보안위협_매트릭스_v5_AI활용공격뷰.xlsx(5시트)·통합_AI활용공격뷰_v5.md·교차 CSV. 기존 통합 빌드와 독립(v4.1 산출물 불변)</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
+          <t>④단계 — 통합본에 Lv0 뷰로 편입(D9), 고유 위협 수 이중계산 방지</t>
         </is>
       </c>
     </row>
@@ -7267,22 +7267,22 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
+          <t>관점 문구(data/text/*.yaml)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
+          <t>35개 행 전부에 핵심 요약·요약설명·참조(■ 관점·■ 실제 사례)·탐지·대응 작성(RT 4·RD 5·VE 5·IA 6·AO 6·CC 4·IM 5). 인용 사례 45건([실제 사고]·[위협인텔]·[실증]), 실제 사고가 없는 8개 행(정찰·역량 확보·방어 회피 등)은 '공개 사고 미확인 — 사유'와 AI 역량 성숙도로 근거 표기. 참고 문헌은 ■ 관점·■ 대응 끝 '참고:' 줄로 인용</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
+          <t>③단계(v2) — 방어 관점(가드레일 D11: 공세 제작법·악용 절차 미기재, 탐지·대응 중심)으로 행마다 근거·통제를 연결</t>
         </is>
       </c>
     </row>
@@ -7299,29 +7299,29 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>시나리오</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py</t>
+          <t>공격 체인 시나리오(data/scenarios.yaml)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
+          <t>실제 사고를 AI 활용 공격 흐름 8개로 재구성(ASN-01~08) — 자율·다중 에이전트 첩보(GTG-1002), 탈옥 모델 자율 하네스(Hermes), AI CLI 악용→클라우드 장악(s1ngularity), 딥페이크 화상회의 송금(Arup), AI 연동 악성코드→AI 서비스 C2(LAMEHUG), 딥페이크 생체 우회, 워크플로 대량 악용→연쇄 침해, LLMjacking·크립토재킹. 19개 단계·초크 포인트 17개</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
+          <t>한 행=한 행위로 나눈 세부위협을 흐름 안에서 보고 차단 지점(초크 포인트)을 드러냄</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
+          <t>scripts/validate.py</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
+          <t>문구·시나리오 검사 이식 — oneline 50자·summary 2줄·■ 관점/실제 사례·■ 탐지/대응 형식, 사례 라벨↔집계 상태·시점·수치 대조, 참조 ID(ATLAS·ATT&amp;CK·OWASP·NIST·연계) 존재·행 매핑, 용어·가드레일(공세 제작법 표현 차단), 시나리오 ID·단계·사고·초크 포인트. 문구 35·시나리오 8을 --strict로 검증해 오류·경고 0</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
+          <t>문구·시나리오의 사례·수치·ID·가드레일을 사고 DB·카탈로그와 기계적으로 대조</t>
         </is>
       </c>
     </row>
@@ -7363,29 +7363,29 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>평가</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>위험평가 결과</t>
+          <t>워크북·CSV(scripts/build_aiattack_threat_matrix.py)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
+          <t>물리·신원 빌드를 이식해 15시트 워크북·CSV 생성(세부위협 35행). AI 활용 공격용으로 고유 축 시트(AI 역할·자율성 × AI 고유성 × 성숙도)·ATLAS/ATT&amp;CK/OWASP 교차 매핑 시트·역매핑 사고사례·평가 기준 시트를 두고, 통합 매트릭스에 고유 축·ATLAS 성숙도·AI 활용 확인/추정 열 추가. 빌드 전 검증기 자동 실행</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
+          <t>②단계(v1) — 분류·근거·평가를 한 워크북에서 검토. 문구·시나리오는 ③단계</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>v0</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -7395,22 +7395,22 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>평가</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>분류 체계(data/taxonomy.yaml)</t>
+          <t>위험평가 결과</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
+          <t>발생가능성 상 12·중 23, 위험도 매우 높음 11·높음 7·보통 16·낮음 1, 근거 수준 실제 사고 확인 22·실사용 역량(성숙도) 7·실증·공개 PoC 6. 우선 위협 1~5위: 단일 자율 공격 에이전트(AIA-AO-01)·AI 가속 자격증명 탈취 확산(AO-05)·워크플로 대량 악용(AO-04)·AI 개발 도구 신뢰 악용(AO-03.2)·피해 단말 AI CLI 악용(AO-03.1). 발생가능성 수식은 다른 매트릭스와 같게 유지(상=실제 사고 2건 이상)하되 AI 역량 성숙도를 보조 신호로 반영(D4), 위협인텔·실증·ATLAS 사례·성숙도는 '중' 상한</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
+          <t>신흥 영역이라 사고가 적은 실증된 역량(자율 취약점 발굴·익스플로잇 생성 등)이 성숙도 신호로 과소평가되지 않게 함</t>
         </is>
       </c>
     </row>
@@ -7427,22 +7427,22 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>사고 DB(data/incidents.yaml)</t>
+          <t>분류 체계(data/taxonomy.yaml)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
+          <t>공격자 킬체인 7개 도메인(RT 정찰·표적 분석 · RD 공격 역량 확보 · VE 취약점 발굴·익스플로잇 생성 · IA 초기 침투·사회공학 · AO 자율 실행·확산 · CC 은닉·명령제어 · IM 영향·규모화) → 위협분류 27개 → 세부위협 35개 ID 대장 확정(AIA-&lt;도메인&gt;-NN). 행마다 킬체인 단계·AI 역할·자율성·AI 고유성(신규/증폭)·AI 역량 성숙도·주체·대상, ATLAS·ATT&amp;CK·OWASP 교차 매핑, NIST 대응 기준, 통합 v4.1 연계 ID, 참고 문헌, 심각도 근거. 심각도 상 17·중 17·하 1. AI 역할 보조 15·반자율 10·증강 7·완전자율 3. 고유성 증폭 20·신규 15</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
+          <t>작업방향 D3·D4 확정(킬체인 축 + AI 역할·자율성·AI 역량 성숙도 축)을 행 단위로 구현 — ①단계</t>
         </is>
       </c>
     </row>
@@ -7459,22 +7459,22 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>교차 매핑</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
+          <t>사고 DB(data/incidents.yaml)</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
+          <t>AI 활용 공격 사고 31건 구축 — 통합 v4.1 'AI 활용=확인/추정' 27건을 origin으로 재인용 + AI 자율 취약점 발굴·익스플로잇 생성 신규 4건(Big Sleep·XBOW·GTIG·CrowdStrike). 집계 실제 사고 24·실증·연구 5·위협인텔 2, AI 활용 확인 28·추정 3, 연도별 2023:3→2024:2→2025:9→2026:17(급증 확인). 실제 사고가 매핑된 세부위협 22/35</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
+          <t>D8(기존 재인용 + 신규) — 최근 급증을 데이터로 드러내고, AI 활용 판정(확인/추정)·역량 성숙도를 사고마다 보존</t>
         </is>
       </c>
     </row>
@@ -7491,22 +7491,22 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>교차 매핑</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>참조 추출본(reference/)</t>
+          <t>프레임워크·참고 문헌(data/frameworks.yaml)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
+          <t>MITRE ATLAS 2026.09(공격자 AI 관점·성숙도), ATT&amp;CK v19.2(AI가 가속하는 기존 기법), OWASP LLM Top 10(2025)·Agentic(악용되는 제3자 AI 측 4개), NIST SP 800-53 Rev.5 통제명, NIST AI RMF(거버넌스 맥락), 참고 문헌 카탈로그 20종(벤더·정부·연구 위협 인텔 — 서지·URL·확인일·이용 조건·확인 경로)</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
+          <t>역할별(교차 매핑·대응 기준·참고 문헌) 출처와 이용 조건을 행 매핑 전에 고정</t>
         </is>
       </c>
     </row>
@@ -7523,22 +7523,22 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>검증</t>
+          <t>근거</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>scripts/validate.py · taxonomy_rules.py</t>
+          <t>참조 추출본(reference/)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+          <t>ATLAS 2026.09 최소 추출본(scripts/prepare_atlas.py — 전술 16·사용 기법 60·사례 73·ID 색인 281, 성숙도 포함), ATT&amp;CK v19.2 추출본(scripts/prepare_attack.py — 기법 37·주체 499·절차 1,036·색인 1,754), NIST 통제명·통합 v4.1 연계 ID 237개(scripts/prepare_refs.py — AI·CL·OT·SC·ID·PH). ATLAS 공개 배포본 원본도 보관(reference/atlas/ATLAS-2026.09.yaml)</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+          <t>빌드·검증을 저장소 안에서 재현. 겹치는 위협은 통합 v4.1 요약 ID로 연계만 함(작업방향 5장·D9)</t>
         </is>
       </c>
     </row>
@@ -7555,20 +7555,52 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
+          <t>검증</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>scripts/validate.py · taxonomy_rules.py</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>검증기를 물리·신원 매트릭스 기준으로 이식 — 분류 체계 필드·어휘·ID 체계, ATLAS·ATT&amp;CK·OWASP·NIST·연계·참고 문헌 키 존재, 사고 DB 필드·어휘·매핑·출처, AI 역할·고유성·성숙도·ai_use 어휘. 데이터 검증 오류 0·경고 0(--strict 통과). 데이터 복사본에 오류 5종을 주입해 검증기가 모두 잡는 것을 확인</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>①단계 완료 기준(매핑·참조 ID 전부 카탈로그에 존재, 검증 데이터 통과) 자동 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>v0</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
           <t>결정</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>작업방향 D3~D9·D11·D12</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>emerging/작업방향.md 10장 권장안을 ①단계 착수 결정으로 확정 — D3(킬체인 7단계+AI 역할·자율성)·D4(발생가능성에 AI 역량 성숙도 신호)·D8(재인용+신규)·D9(통합본 뷰 Lv0, ④단계)·D11(방어 자료 가드레일)·D12(v4.1 베이스라인). D5~D7은 영역 2(enterprise) 결정이라 영역 2 착수 시 확정</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>사용자 지침 — 남은 결정은 착수 시 확정</t>
         </is>
